--- a/data/cox_xlsx/KLEEb.CO.xlsx
+++ b/data/cox_xlsx/KLEEb.CO.xlsx
@@ -246,7 +246,7 @@
     <t>Administration Expenses</t>
   </si>
   <si>
-    <t>Administrative Expenses</t>
+    <t>Administrative Expenses (not use)</t>
   </si>
   <si>
     <t>Reported Operating Expense</t>
@@ -1137,7 +1137,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1200,6 +1200,9 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="6" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="7" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -2646,7 +2649,7 @@
       <c r="R34" s="15"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="14" t="s">
+      <c r="A35" s="21" t="s">
         <v>75</v>
       </c>
       <c r="B35" s="17">
@@ -2961,49 +2964,49 @@
       <c r="A42" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="B42" s="21">
+      <c r="B42" s="22">
         <v>-4.74</v>
       </c>
-      <c r="C42" s="21">
+      <c r="C42" s="22">
         <v>-4.61</v>
       </c>
-      <c r="D42" s="21">
+      <c r="D42" s="22">
         <v>-2.26</v>
       </c>
-      <c r="E42" s="21">
+      <c r="E42" s="22">
         <v>-1.58</v>
       </c>
-      <c r="F42" s="21">
+      <c r="F42" s="22">
         <v>-1.58</v>
       </c>
-      <c r="G42" s="21">
+      <c r="G42" s="22">
         <v>-1.26</v>
       </c>
-      <c r="H42" s="21">
+      <c r="H42" s="22">
         <v>-1.15</v>
       </c>
-      <c r="I42" s="21">
+      <c r="I42" s="22">
         <v>-1.1</v>
       </c>
-      <c r="J42" s="21">
+      <c r="J42" s="22">
         <v>-1.07</v>
       </c>
-      <c r="K42" s="21">
+      <c r="K42" s="22">
         <v>-1.14</v>
       </c>
-      <c r="L42" s="21">
+      <c r="L42" s="22">
         <v>-0.93</v>
       </c>
-      <c r="M42" s="21">
+      <c r="M42" s="22">
         <v>-0.59</v>
       </c>
-      <c r="N42" s="21">
+      <c r="N42" s="22">
         <v>-0.88</v>
       </c>
-      <c r="O42" s="21">
+      <c r="O42" s="22">
         <v>-0.82</v>
       </c>
-      <c r="P42" s="21">
+      <c r="P42" s="22">
         <v>-0.75</v>
       </c>
       <c r="Q42" s="15"/>
@@ -3013,46 +3016,46 @@
       <c r="A43" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="B43" s="21">
+      <c r="B43" s="22">
         <v>-0.3</v>
       </c>
-      <c r="C43" s="21">
+      <c r="C43" s="22">
         <v>-0.37</v>
       </c>
-      <c r="D43" s="21">
+      <c r="D43" s="22">
         <v>-0.35</v>
       </c>
-      <c r="E43" s="21">
+      <c r="E43" s="22">
         <v>-0.32</v>
       </c>
-      <c r="F43" s="21">
+      <c r="F43" s="22">
         <v>-0.38</v>
       </c>
-      <c r="G43" s="21">
+      <c r="G43" s="22">
         <v>-0.42</v>
       </c>
-      <c r="H43" s="21">
+      <c r="H43" s="22">
         <v>-0.43</v>
       </c>
-      <c r="I43" s="21">
+      <c r="I43" s="22">
         <v>-0.46</v>
       </c>
-      <c r="J43" s="21">
+      <c r="J43" s="22">
         <v>-0.46</v>
       </c>
-      <c r="K43" s="21">
+      <c r="K43" s="22">
         <v>-0.5</v>
       </c>
-      <c r="L43" s="21">
+      <c r="L43" s="22">
         <v>-0.41</v>
       </c>
-      <c r="M43" s="21">
+      <c r="M43" s="22">
         <v>-0.22</v>
       </c>
-      <c r="N43" s="21">
+      <c r="N43" s="22">
         <v>-0.27</v>
       </c>
-      <c r="O43" s="21">
+      <c r="O43" s="22">
         <v>-0.43</v>
       </c>
       <c r="P43" s="15"/>
@@ -3063,22 +3066,22 @@
       <c r="A44" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="B44" s="21">
+      <c r="B44" s="22">
         <v>-2.27</v>
       </c>
-      <c r="C44" s="21">
+      <c r="C44" s="22">
         <v>-2.12</v>
       </c>
-      <c r="D44" s="21">
+      <c r="D44" s="22">
         <v>-0.56</v>
       </c>
-      <c r="E44" s="21">
+      <c r="E44" s="22">
         <v>-0.3</v>
       </c>
-      <c r="F44" s="21">
+      <c r="F44" s="22">
         <v>-0.15</v>
       </c>
-      <c r="G44" s="21">
+      <c r="G44" s="22">
         <v>-0.2</v>
       </c>
       <c r="H44" s="15"/>
@@ -3097,13 +3100,13 @@
       <c r="A45" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="B45" s="21">
+      <c r="B45" s="22">
         <v>-0.66</v>
       </c>
-      <c r="C45" s="21">
+      <c r="C45" s="22">
         <v>-0.68</v>
       </c>
-      <c r="D45" s="21">
+      <c r="D45" s="22">
         <v>-0.76</v>
       </c>
       <c r="E45" s="15"/>
@@ -3111,22 +3114,22 @@
       <c r="G45" s="15"/>
       <c r="H45" s="15"/>
       <c r="I45" s="15"/>
-      <c r="J45" s="21">
+      <c r="J45" s="22">
         <v>-0.24</v>
       </c>
-      <c r="K45" s="21">
+      <c r="K45" s="22">
         <v>-0.28</v>
       </c>
-      <c r="L45" s="21">
+      <c r="L45" s="22">
         <v>-0.2</v>
       </c>
-      <c r="M45" s="21">
+      <c r="M45" s="22">
         <v>-0.13</v>
       </c>
-      <c r="N45" s="21">
+      <c r="N45" s="22">
         <v>-0.08</v>
       </c>
-      <c r="O45" s="21">
+      <c r="O45" s="22">
         <v>-0.07</v>
       </c>
       <c r="P45" s="15"/>
@@ -3137,46 +3140,46 @@
       <c r="A46" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="B46" s="21">
+      <c r="B46" s="22">
         <v>-1.52</v>
       </c>
-      <c r="C46" s="21">
+      <c r="C46" s="22">
         <v>-1.45</v>
       </c>
-      <c r="D46" s="21">
+      <c r="D46" s="22">
         <v>-0.6</v>
       </c>
-      <c r="E46" s="21">
+      <c r="E46" s="22">
         <v>-0.96</v>
       </c>
-      <c r="F46" s="21">
+      <c r="F46" s="22">
         <v>-1.05</v>
       </c>
-      <c r="G46" s="21">
+      <c r="G46" s="22">
         <v>-0.64</v>
       </c>
-      <c r="H46" s="21">
+      <c r="H46" s="22">
         <v>-0.72</v>
       </c>
-      <c r="I46" s="21">
+      <c r="I46" s="22">
         <v>-0.65</v>
       </c>
-      <c r="J46" s="21">
+      <c r="J46" s="22">
         <v>-0.37</v>
       </c>
-      <c r="K46" s="21">
+      <c r="K46" s="22">
         <v>-0.36</v>
       </c>
-      <c r="L46" s="21">
+      <c r="L46" s="22">
         <v>-0.31</v>
       </c>
-      <c r="M46" s="21">
+      <c r="M46" s="22">
         <v>-0.25</v>
       </c>
-      <c r="N46" s="21">
+      <c r="N46" s="22">
         <v>-0.53</v>
       </c>
-      <c r="O46" s="21">
+      <c r="O46" s="22">
         <v>-0.32</v>
       </c>
       <c r="P46" s="15"/>
@@ -3202,10 +3205,10 @@
       <c r="N47" s="15"/>
       <c r="O47" s="15"/>
       <c r="P47" s="15"/>
-      <c r="Q47" s="21">
+      <c r="Q47" s="22">
         <v>-0.85</v>
       </c>
-      <c r="R47" s="21">
+      <c r="R47" s="22">
         <v>-0.93</v>
       </c>
     </row>
@@ -3239,55 +3242,55 @@
       <c r="A49" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="B49" s="22">
+      <c r="B49" s="23">
         <v>-4.03</v>
       </c>
-      <c r="C49" s="22">
+      <c r="C49" s="23">
         <v>-4.02</v>
       </c>
-      <c r="D49" s="22">
+      <c r="D49" s="23">
         <v>-1.96</v>
       </c>
-      <c r="E49" s="22">
+      <c r="E49" s="23">
         <v>-1.11</v>
       </c>
-      <c r="F49" s="22">
+      <c r="F49" s="23">
         <v>-1.43</v>
       </c>
-      <c r="G49" s="22">
+      <c r="G49" s="23">
         <v>-1.15</v>
       </c>
-      <c r="H49" s="22">
+      <c r="H49" s="23">
         <v>-1.1</v>
       </c>
-      <c r="I49" s="22">
+      <c r="I49" s="23">
         <v>-1.02</v>
       </c>
-      <c r="J49" s="22">
+      <c r="J49" s="23">
         <v>-0.95</v>
       </c>
-      <c r="K49" s="22">
+      <c r="K49" s="23">
         <v>-1.01</v>
       </c>
-      <c r="L49" s="22">
+      <c r="L49" s="23">
         <v>-0.76</v>
       </c>
-      <c r="M49" s="22">
+      <c r="M49" s="23">
         <v>-0.57</v>
       </c>
-      <c r="N49" s="22">
+      <c r="N49" s="23">
         <v>-0.86</v>
       </c>
-      <c r="O49" s="22">
+      <c r="O49" s="23">
         <v>-0.81</v>
       </c>
-      <c r="P49" s="22">
+      <c r="P49" s="23">
         <v>-0.66</v>
       </c>
-      <c r="Q49" s="22">
+      <c r="Q49" s="23">
         <v>-0.67</v>
       </c>
-      <c r="R49" s="22">
+      <c r="R49" s="23">
         <v>-0.6</v>
       </c>
     </row>
@@ -3297,7 +3300,7 @@
       </c>
       <c r="B50" s="15"/>
       <c r="C50" s="15"/>
-      <c r="D50" s="23">
+      <c r="D50" s="24">
         <v>0.0</v>
       </c>
       <c r="E50" s="15"/>
@@ -3367,7 +3370,7 @@
       <c r="Q51" s="20">
         <v>10.8</v>
       </c>
-      <c r="R51" s="22">
+      <c r="R51" s="23">
         <v>-0.44</v>
       </c>
     </row>
@@ -3475,10 +3478,10 @@
       <c r="O54" s="17">
         <v>3.17</v>
       </c>
-      <c r="P54" s="21">
+      <c r="P54" s="22">
         <v>-3.26</v>
       </c>
-      <c r="Q54" s="21">
+      <c r="Q54" s="22">
         <v>-1.04</v>
       </c>
       <c r="R54" s="15">
@@ -3493,7 +3496,7 @@
       <c r="C55" s="15"/>
       <c r="D55" s="15"/>
       <c r="E55" s="15"/>
-      <c r="F55" s="21">
+      <c r="F55" s="22">
         <v>-0.46</v>
       </c>
       <c r="G55" s="15"/>
@@ -3503,19 +3506,19 @@
       <c r="K55" s="15"/>
       <c r="L55" s="15"/>
       <c r="M55" s="15"/>
-      <c r="N55" s="21">
+      <c r="N55" s="22">
         <v>-0.4</v>
       </c>
-      <c r="O55" s="21">
+      <c r="O55" s="22">
         <v>-0.03</v>
       </c>
       <c r="P55" s="17">
         <v>0.03</v>
       </c>
-      <c r="Q55" s="21">
+      <c r="Q55" s="22">
         <v>-1.63</v>
       </c>
-      <c r="R55" s="21">
+      <c r="R55" s="22">
         <v>-0.08</v>
       </c>
     </row>
@@ -3547,7 +3550,7 @@
         <v>0.08</v>
       </c>
       <c r="Q56" s="15"/>
-      <c r="R56" s="21">
+      <c r="R56" s="22">
         <v>-0.02</v>
       </c>
     </row>
@@ -3659,7 +3662,7 @@
       <c r="Q58" s="20">
         <v>8.13</v>
       </c>
-      <c r="R58" s="22">
+      <c r="R58" s="23">
         <v>-0.53</v>
       </c>
     </row>
@@ -3715,7 +3718,7 @@
       <c r="Q59" s="20">
         <v>8.13</v>
       </c>
-      <c r="R59" s="22">
+      <c r="R59" s="23">
         <v>-0.53</v>
       </c>
     </row>
@@ -3780,16 +3783,16 @@
       <c r="H61" s="20">
         <v>0.98</v>
       </c>
-      <c r="I61" s="24"/>
-      <c r="J61" s="24"/>
-      <c r="K61" s="24"/>
-      <c r="L61" s="24"/>
-      <c r="M61" s="24"/>
-      <c r="N61" s="24"/>
-      <c r="O61" s="24"/>
-      <c r="P61" s="24"/>
-      <c r="Q61" s="24"/>
-      <c r="R61" s="24"/>
+      <c r="I61" s="25"/>
+      <c r="J61" s="25"/>
+      <c r="K61" s="25"/>
+      <c r="L61" s="25"/>
+      <c r="M61" s="25"/>
+      <c r="N61" s="25"/>
+      <c r="O61" s="25"/>
+      <c r="P61" s="25"/>
+      <c r="Q61" s="25"/>
+      <c r="R61" s="25"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="18" t="s">
@@ -3843,7 +3846,7 @@
       <c r="Q62" s="20">
         <v>8.13</v>
       </c>
-      <c r="R62" s="22">
+      <c r="R62" s="23">
         <v>-0.53</v>
       </c>
     </row>
@@ -3899,7 +3902,7 @@
       <c r="Q63" s="20">
         <v>8.13</v>
       </c>
-      <c r="R63" s="22">
+      <c r="R63" s="23">
         <v>-0.53</v>
       </c>
     </row>
@@ -3979,7 +3982,7 @@
       <c r="Q65" s="20">
         <v>8.13</v>
       </c>
-      <c r="R65" s="22">
+      <c r="R65" s="23">
         <v>-0.53</v>
       </c>
     </row>
@@ -4147,7 +4150,7 @@
       <c r="Q68" s="16">
         <v>159.69</v>
       </c>
-      <c r="R68" s="21">
+      <c r="R68" s="22">
         <v>-10.48</v>
       </c>
     </row>
@@ -4203,7 +4206,7 @@
       <c r="Q69" s="16">
         <v>159.69</v>
       </c>
-      <c r="R69" s="21">
+      <c r="R69" s="22">
         <v>-10.48</v>
       </c>
     </row>
@@ -4259,7 +4262,7 @@
       <c r="Q70" s="17">
         <v>8.13</v>
       </c>
-      <c r="R70" s="21">
+      <c r="R70" s="22">
         <v>-0.53</v>
       </c>
     </row>
@@ -4315,7 +4318,7 @@
       <c r="Q71" s="16">
         <v>159.2</v>
       </c>
-      <c r="R71" s="21">
+      <c r="R71" s="22">
         <v>-10.44</v>
       </c>
     </row>
@@ -4371,7 +4374,7 @@
       <c r="Q72" s="17">
         <v>8.13</v>
       </c>
-      <c r="R72" s="21">
+      <c r="R72" s="22">
         <v>-0.53</v>
       </c>
     </row>
@@ -4427,7 +4430,7 @@
       <c r="Q73" s="16">
         <v>159.2</v>
       </c>
-      <c r="R73" s="21">
+      <c r="R73" s="22">
         <v>-10.44</v>
       </c>
     </row>
@@ -6678,11 +6681,11 @@
       <c r="A26" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="B26" s="23">
+      <c r="B26" s="24">
         <v>0.0</v>
       </c>
       <c r="C26" s="15"/>
-      <c r="D26" s="23">
+      <c r="D26" s="24">
         <v>0.0</v>
       </c>
       <c r="E26" s="15"/>
@@ -6980,19 +6983,19 @@
       <c r="K33" s="15"/>
       <c r="L33" s="15"/>
       <c r="M33" s="15"/>
-      <c r="N33" s="21">
+      <c r="N33" s="22">
         <v>-6.62</v>
       </c>
-      <c r="O33" s="21">
+      <c r="O33" s="22">
         <v>-5.23</v>
       </c>
-      <c r="P33" s="21">
+      <c r="P33" s="22">
         <v>-4.78</v>
       </c>
-      <c r="Q33" s="21">
+      <c r="Q33" s="22">
         <v>-4.02</v>
       </c>
-      <c r="R33" s="21">
+      <c r="R33" s="22">
         <v>-3.37</v>
       </c>
     </row>
@@ -7052,11 +7055,11 @@
       <c r="A36" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="B36" s="23">
+      <c r="B36" s="24">
         <v>0.0</v>
       </c>
       <c r="C36" s="15"/>
-      <c r="D36" s="23">
+      <c r="D36" s="24">
         <v>0.0</v>
       </c>
       <c r="E36" s="15"/>
@@ -7090,19 +7093,19 @@
       <c r="K37" s="15"/>
       <c r="L37" s="15"/>
       <c r="M37" s="15"/>
-      <c r="N37" s="21">
+      <c r="N37" s="22">
         <v>-6.62</v>
       </c>
-      <c r="O37" s="21">
+      <c r="O37" s="22">
         <v>-5.23</v>
       </c>
-      <c r="P37" s="21">
+      <c r="P37" s="22">
         <v>-4.78</v>
       </c>
-      <c r="Q37" s="21">
+      <c r="Q37" s="22">
         <v>-4.02</v>
       </c>
-      <c r="R37" s="21">
+      <c r="R37" s="22">
         <v>-3.37</v>
       </c>
     </row>
@@ -7178,7 +7181,7 @@
       <c r="K40" s="15"/>
       <c r="L40" s="15"/>
       <c r="M40" s="15"/>
-      <c r="N40" s="21">
+      <c r="N40" s="22">
         <v>-15.38</v>
       </c>
       <c r="O40" s="15"/>
@@ -7202,19 +7205,19 @@
       <c r="K41" s="15"/>
       <c r="L41" s="15"/>
       <c r="M41" s="15"/>
-      <c r="N41" s="21">
+      <c r="N41" s="22">
         <v>-29.35</v>
       </c>
-      <c r="O41" s="21">
+      <c r="O41" s="22">
         <v>-25.76</v>
       </c>
-      <c r="P41" s="21">
+      <c r="P41" s="22">
         <v>-28.33</v>
       </c>
-      <c r="Q41" s="21">
+      <c r="Q41" s="22">
         <v>-27.1</v>
       </c>
-      <c r="R41" s="21">
+      <c r="R41" s="22">
         <v>-27.47</v>
       </c>
     </row>
@@ -7394,7 +7397,7 @@
       <c r="K46" s="15"/>
       <c r="L46" s="15"/>
       <c r="M46" s="15"/>
-      <c r="N46" s="21">
+      <c r="N46" s="22">
         <v>-13.97</v>
       </c>
       <c r="O46" s="15"/>
@@ -7647,7 +7650,7 @@
         <v>162</v>
       </c>
       <c r="B53" s="15"/>
-      <c r="C53" s="23">
+      <c r="C53" s="24">
         <v>0.0</v>
       </c>
       <c r="D53" s="15"/>
@@ -8461,7 +8464,7 @@
         <v>182</v>
       </c>
       <c r="B73" s="15"/>
-      <c r="C73" s="23">
+      <c r="C73" s="24">
         <v>0.0</v>
       </c>
       <c r="D73" s="15">
@@ -8722,28 +8725,28 @@
       <c r="E78" s="17">
         <v>0.84</v>
       </c>
-      <c r="F78" s="21">
+      <c r="F78" s="22">
         <v>-0.67</v>
       </c>
-      <c r="G78" s="21">
+      <c r="G78" s="22">
         <v>-1.26</v>
       </c>
-      <c r="H78" s="21">
+      <c r="H78" s="22">
         <v>-1.47</v>
       </c>
-      <c r="I78" s="21">
+      <c r="I78" s="22">
         <v>-0.7</v>
       </c>
-      <c r="J78" s="21">
+      <c r="J78" s="22">
         <v>-0.83</v>
       </c>
-      <c r="K78" s="21">
+      <c r="K78" s="22">
         <v>-1.33</v>
       </c>
-      <c r="L78" s="21">
+      <c r="L78" s="22">
         <v>-0.68</v>
       </c>
-      <c r="M78" s="21">
+      <c r="M78" s="22">
         <v>-0.52</v>
       </c>
       <c r="N78" s="15"/>
@@ -8824,10 +8827,10 @@
       <c r="K80" s="15"/>
       <c r="L80" s="15"/>
       <c r="M80" s="15"/>
-      <c r="N80" s="21">
+      <c r="N80" s="22">
         <v>-0.08</v>
       </c>
-      <c r="O80" s="21">
+      <c r="O80" s="22">
         <v>-0.02</v>
       </c>
       <c r="P80" s="15">
@@ -8852,7 +8855,7 @@
       <c r="K81" s="15"/>
       <c r="L81" s="15"/>
       <c r="M81" s="15"/>
-      <c r="N81" s="21">
+      <c r="N81" s="22">
         <v>-0.08</v>
       </c>
       <c r="O81" s="15"/>
@@ -8890,7 +8893,7 @@
       </c>
       <c r="B83" s="15"/>
       <c r="C83" s="15"/>
-      <c r="D83" s="23">
+      <c r="D83" s="24">
         <v>0.0</v>
       </c>
       <c r="E83" s="15"/>
@@ -9025,16 +9028,16 @@
       <c r="H86" s="20">
         <v>1.87</v>
       </c>
-      <c r="I86" s="24"/>
-      <c r="J86" s="24"/>
-      <c r="K86" s="24"/>
-      <c r="L86" s="24"/>
-      <c r="M86" s="24"/>
-      <c r="N86" s="24"/>
-      <c r="O86" s="24"/>
-      <c r="P86" s="24"/>
-      <c r="Q86" s="24"/>
-      <c r="R86" s="24"/>
+      <c r="I86" s="25"/>
+      <c r="J86" s="25"/>
+      <c r="K86" s="25"/>
+      <c r="L86" s="25"/>
+      <c r="M86" s="25"/>
+      <c r="N86" s="25"/>
+      <c r="O86" s="25"/>
+      <c r="P86" s="25"/>
+      <c r="Q86" s="25"/>
+      <c r="R86" s="25"/>
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="18" t="s">
@@ -11643,13 +11646,13 @@
       <c r="K20" s="15"/>
       <c r="L20" s="15"/>
       <c r="M20" s="15"/>
-      <c r="N20" s="23">
+      <c r="N20" s="24">
         <v>0.0</v>
       </c>
       <c r="O20" s="15">
         <v>0.0</v>
       </c>
-      <c r="P20" s="23">
+      <c r="P20" s="24">
         <v>0.0</v>
       </c>
       <c r="Q20" s="15">
@@ -11675,19 +11678,19 @@
       <c r="K21" s="15"/>
       <c r="L21" s="15"/>
       <c r="M21" s="15"/>
-      <c r="N21" s="21">
+      <c r="N21" s="22">
         <v>-0.02</v>
       </c>
-      <c r="O21" s="21">
+      <c r="O21" s="22">
         <v>-0.01</v>
       </c>
-      <c r="P21" s="21">
+      <c r="P21" s="22">
         <v>-0.09</v>
       </c>
-      <c r="Q21" s="21">
+      <c r="Q21" s="22">
         <v>-0.18</v>
       </c>
-      <c r="R21" s="21">
+      <c r="R21" s="22">
         <v>-0.33</v>
       </c>
     </row>
@@ -11774,10 +11777,10 @@
       <c r="N24" s="17">
         <v>4.82</v>
       </c>
-      <c r="O24" s="21">
+      <c r="O24" s="22">
         <v>-1.16</v>
       </c>
-      <c r="P24" s="21">
+      <c r="P24" s="22">
         <v>-10.37</v>
       </c>
       <c r="Q24" s="17">
@@ -11803,10 +11806,10 @@
       <c r="K25" s="15"/>
       <c r="L25" s="15"/>
       <c r="M25" s="15"/>
-      <c r="N25" s="21">
+      <c r="N25" s="22">
         <v>-1.67</v>
       </c>
-      <c r="O25" s="21">
+      <c r="O25" s="22">
         <v>-1.31</v>
       </c>
       <c r="P25" s="17">
@@ -11815,7 +11818,7 @@
       <c r="Q25" s="17">
         <v>3.1</v>
       </c>
-      <c r="R25" s="21">
+      <c r="R25" s="22">
         <v>-6.88</v>
       </c>
     </row>
@@ -11838,13 +11841,13 @@
       <c r="N26" s="17">
         <v>1.49</v>
       </c>
-      <c r="O26" s="21">
+      <c r="O26" s="22">
         <v>-1.21</v>
       </c>
-      <c r="P26" s="21">
+      <c r="P26" s="22">
         <v>-5.77</v>
       </c>
-      <c r="Q26" s="21">
+      <c r="Q26" s="22">
         <v>-4.43</v>
       </c>
       <c r="R26" s="17">
@@ -11867,7 +11870,7 @@
       <c r="K27" s="15"/>
       <c r="L27" s="15"/>
       <c r="M27" s="15"/>
-      <c r="N27" s="21">
+      <c r="N27" s="22">
         <v>-0.07</v>
       </c>
       <c r="O27" s="15"/>
@@ -12005,7 +12008,7 @@
       <c r="Q30" s="17">
         <v>8.13</v>
       </c>
-      <c r="R30" s="21">
+      <c r="R30" s="22">
         <v>-0.53</v>
       </c>
     </row>
@@ -12163,10 +12166,10 @@
       <c r="C34" s="17">
         <v>1.13</v>
       </c>
-      <c r="D34" s="21">
+      <c r="D34" s="22">
         <v>-7.47</v>
       </c>
-      <c r="E34" s="21">
+      <c r="E34" s="22">
         <v>-27.34</v>
       </c>
       <c r="F34" s="17">
@@ -12175,22 +12178,22 @@
       <c r="G34" s="17">
         <v>17.44</v>
       </c>
-      <c r="H34" s="21">
+      <c r="H34" s="22">
         <v>-16.78</v>
       </c>
-      <c r="I34" s="21">
+      <c r="I34" s="22">
         <v>-2.37</v>
       </c>
       <c r="J34" s="17">
         <v>2.17</v>
       </c>
-      <c r="K34" s="21">
+      <c r="K34" s="22">
         <v>-10.17</v>
       </c>
-      <c r="L34" s="21">
+      <c r="L34" s="22">
         <v>-6.82</v>
       </c>
-      <c r="M34" s="21">
+      <c r="M34" s="22">
         <v>-0.26</v>
       </c>
       <c r="N34" s="15"/>
@@ -12259,55 +12262,55 @@
       <c r="A36" s="14" t="s">
         <v>219</v>
       </c>
-      <c r="B36" s="21">
+      <c r="B36" s="22">
         <v>-4.74</v>
       </c>
-      <c r="C36" s="21">
+      <c r="C36" s="22">
         <v>-4.61</v>
       </c>
-      <c r="D36" s="21">
+      <c r="D36" s="22">
         <v>-2.26</v>
       </c>
-      <c r="E36" s="21">
+      <c r="E36" s="22">
         <v>-1.58</v>
       </c>
-      <c r="F36" s="21">
+      <c r="F36" s="22">
         <v>-1.58</v>
       </c>
-      <c r="G36" s="21">
+      <c r="G36" s="22">
         <v>-1.26</v>
       </c>
-      <c r="H36" s="21">
+      <c r="H36" s="22">
         <v>-1.3</v>
       </c>
-      <c r="I36" s="21">
+      <c r="I36" s="22">
         <v>-1.1</v>
       </c>
-      <c r="J36" s="21">
+      <c r="J36" s="22">
         <v>-1.08</v>
       </c>
-      <c r="K36" s="21">
+      <c r="K36" s="22">
         <v>-1.19</v>
       </c>
-      <c r="L36" s="21">
+      <c r="L36" s="22">
         <v>-0.95</v>
       </c>
-      <c r="M36" s="21">
+      <c r="M36" s="22">
         <v>-0.6</v>
       </c>
-      <c r="N36" s="21">
+      <c r="N36" s="22">
         <v>-0.88</v>
       </c>
-      <c r="O36" s="21">
+      <c r="O36" s="22">
         <v>-0.82</v>
       </c>
-      <c r="P36" s="21">
+      <c r="P36" s="22">
         <v>-0.76</v>
       </c>
-      <c r="Q36" s="21">
+      <c r="Q36" s="22">
         <v>-0.85</v>
       </c>
-      <c r="R36" s="21">
+      <c r="R36" s="22">
         <v>-0.92</v>
       </c>
     </row>
@@ -12339,55 +12342,55 @@
       <c r="A38" s="14" t="s">
         <v>231</v>
       </c>
-      <c r="B38" s="21">
+      <c r="B38" s="22">
         <v>-8.39</v>
       </c>
-      <c r="C38" s="21">
+      <c r="C38" s="22">
         <v>-6.87</v>
       </c>
-      <c r="D38" s="21">
+      <c r="D38" s="22">
         <v>-11.01</v>
       </c>
-      <c r="E38" s="21">
+      <c r="E38" s="22">
         <v>-5.76</v>
       </c>
-      <c r="F38" s="21">
+      <c r="F38" s="22">
         <v>-1.95</v>
       </c>
-      <c r="G38" s="21">
+      <c r="G38" s="22">
         <v>-2.95</v>
       </c>
-      <c r="H38" s="21">
+      <c r="H38" s="22">
         <v>-4.64</v>
       </c>
-      <c r="I38" s="21">
+      <c r="I38" s="22">
         <v>-4.48</v>
       </c>
-      <c r="J38" s="21">
+      <c r="J38" s="22">
         <v>-4.86</v>
       </c>
-      <c r="K38" s="21">
+      <c r="K38" s="22">
         <v>-2.74</v>
       </c>
-      <c r="L38" s="21">
+      <c r="L38" s="22">
         <v>-4.11</v>
       </c>
-      <c r="M38" s="21">
+      <c r="M38" s="22">
         <v>-2.17</v>
       </c>
-      <c r="N38" s="21">
+      <c r="N38" s="22">
         <v>-2.13</v>
       </c>
-      <c r="O38" s="21">
+      <c r="O38" s="22">
         <v>-3.23</v>
       </c>
-      <c r="P38" s="21">
+      <c r="P38" s="22">
         <v>-1.79</v>
       </c>
       <c r="Q38" s="15">
         <v>0.0</v>
       </c>
-      <c r="R38" s="21">
+      <c r="R38" s="22">
         <v>-4.23</v>
       </c>
     </row>
@@ -12412,7 +12415,7 @@
       <c r="P39" s="15">
         <v>0.0</v>
       </c>
-      <c r="Q39" s="21">
+      <c r="Q39" s="22">
         <v>-15.0</v>
       </c>
       <c r="R39" s="15"/>
@@ -12477,16 +12480,16 @@
       <c r="A41" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="B41" s="23">
-        <v>0.0</v>
-      </c>
-      <c r="C41" s="21">
+      <c r="B41" s="24">
+        <v>0.0</v>
+      </c>
+      <c r="C41" s="22">
         <v>-0.58</v>
       </c>
-      <c r="D41" s="21">
+      <c r="D41" s="22">
         <v>-0.02</v>
       </c>
-      <c r="E41" s="21">
+      <c r="E41" s="22">
         <v>-0.26</v>
       </c>
       <c r="F41" s="15">
@@ -12495,13 +12498,13 @@
       <c r="G41" s="15">
         <v>0.0</v>
       </c>
-      <c r="H41" s="21">
+      <c r="H41" s="22">
         <v>-0.01</v>
       </c>
-      <c r="I41" s="21">
+      <c r="I41" s="22">
         <v>-0.01</v>
       </c>
-      <c r="J41" s="21">
+      <c r="J41" s="22">
         <v>-0.01</v>
       </c>
       <c r="K41" s="15">
@@ -12513,7 +12516,7 @@
       <c r="M41" s="15">
         <v>0.0</v>
       </c>
-      <c r="N41" s="23">
+      <c r="N41" s="24">
         <v>0.0</v>
       </c>
       <c r="O41" s="15"/>
@@ -12525,55 +12528,55 @@
       <c r="A42" s="14" t="s">
         <v>233</v>
       </c>
-      <c r="B42" s="21">
+      <c r="B42" s="22">
         <v>-2.06</v>
       </c>
-      <c r="C42" s="21">
+      <c r="C42" s="22">
         <v>-1.68</v>
       </c>
-      <c r="D42" s="21">
+      <c r="D42" s="22">
         <v>-2.82</v>
       </c>
-      <c r="E42" s="21">
+      <c r="E42" s="22">
         <v>-0.51</v>
       </c>
       <c r="F42" s="15">
         <v>0.0</v>
       </c>
-      <c r="G42" s="21">
+      <c r="G42" s="22">
         <v>-3.19</v>
       </c>
-      <c r="H42" s="21">
+      <c r="H42" s="22">
         <v>-6.49</v>
       </c>
-      <c r="I42" s="21">
+      <c r="I42" s="22">
         <v>-0.01</v>
       </c>
-      <c r="J42" s="21">
+      <c r="J42" s="22">
         <v>-0.54</v>
       </c>
       <c r="K42" s="15">
         <v>0.0</v>
       </c>
-      <c r="L42" s="21">
+      <c r="L42" s="22">
         <v>-0.67</v>
       </c>
-      <c r="M42" s="21">
+      <c r="M42" s="22">
         <v>-0.78</v>
       </c>
-      <c r="N42" s="21">
+      <c r="N42" s="22">
         <v>-0.25</v>
       </c>
-      <c r="O42" s="21">
+      <c r="O42" s="22">
         <v>-0.01</v>
       </c>
-      <c r="P42" s="21">
+      <c r="P42" s="22">
         <v>-0.16</v>
       </c>
-      <c r="Q42" s="21">
+      <c r="Q42" s="22">
         <v>-0.12</v>
       </c>
-      <c r="R42" s="21">
+      <c r="R42" s="22">
         <v>-2.73</v>
       </c>
     </row>
@@ -12581,55 +12584,55 @@
       <c r="A43" s="14" t="s">
         <v>234</v>
       </c>
-      <c r="B43" s="21">
+      <c r="B43" s="22">
         <v>-4.54</v>
       </c>
-      <c r="C43" s="21">
+      <c r="C43" s="22">
         <v>-2.46</v>
       </c>
-      <c r="D43" s="21">
+      <c r="D43" s="22">
         <v>-1.85</v>
       </c>
-      <c r="E43" s="21">
+      <c r="E43" s="22">
         <v>-3.51</v>
       </c>
-      <c r="F43" s="21">
+      <c r="F43" s="22">
         <v>-1.21</v>
       </c>
-      <c r="G43" s="21">
+      <c r="G43" s="22">
         <v>-1.09</v>
       </c>
-      <c r="H43" s="21">
+      <c r="H43" s="22">
         <v>-1.58</v>
       </c>
-      <c r="I43" s="21">
+      <c r="I43" s="22">
         <v>-8.57</v>
       </c>
-      <c r="J43" s="21">
+      <c r="J43" s="22">
         <v>-2.44</v>
       </c>
-      <c r="K43" s="21">
+      <c r="K43" s="22">
         <v>-3.37</v>
       </c>
-      <c r="L43" s="21">
+      <c r="L43" s="22">
         <v>-12.79</v>
       </c>
-      <c r="M43" s="21">
+      <c r="M43" s="22">
         <v>-1.1</v>
       </c>
-      <c r="N43" s="21">
+      <c r="N43" s="22">
         <v>-0.87</v>
       </c>
-      <c r="O43" s="21">
+      <c r="O43" s="22">
         <v>-1.62</v>
       </c>
-      <c r="P43" s="21">
+      <c r="P43" s="22">
         <v>-1.91</v>
       </c>
-      <c r="Q43" s="21">
+      <c r="Q43" s="22">
         <v>-2.65</v>
       </c>
-      <c r="R43" s="21">
+      <c r="R43" s="22">
         <v>-4.04</v>
       </c>
     </row>
@@ -12717,7 +12720,7 @@
       <c r="O45" s="15">
         <v>0.0</v>
       </c>
-      <c r="P45" s="21">
+      <c r="P45" s="22">
         <v>-0.03</v>
       </c>
       <c r="Q45" s="15"/>
@@ -12730,20 +12733,20 @@
       <c r="B46" s="15">
         <v>0.0</v>
       </c>
-      <c r="C46" s="21">
+      <c r="C46" s="22">
         <v>-34.52</v>
       </c>
       <c r="D46" s="15">
         <v>0.0</v>
       </c>
-      <c r="E46" s="21">
+      <c r="E46" s="22">
         <v>-3.69</v>
       </c>
       <c r="F46" s="15"/>
       <c r="G46" s="15">
         <v>0.0</v>
       </c>
-      <c r="H46" s="21">
+      <c r="H46" s="22">
         <v>-3.28</v>
       </c>
       <c r="I46" s="15"/>
@@ -12774,10 +12777,10 @@
       <c r="L47" s="15"/>
       <c r="M47" s="15"/>
       <c r="N47" s="15"/>
-      <c r="O47" s="21">
+      <c r="O47" s="22">
         <v>-0.01</v>
       </c>
-      <c r="P47" s="21">
+      <c r="P47" s="22">
         <v>-0.1</v>
       </c>
       <c r="Q47" s="15"/>
@@ -12788,7 +12791,7 @@
         <v>239</v>
       </c>
       <c r="B48" s="15"/>
-      <c r="C48" s="23">
+      <c r="C48" s="24">
         <v>0.0</v>
       </c>
       <c r="D48" s="15">
@@ -12815,55 +12818,55 @@
       <c r="A49" s="18" t="s">
         <v>240</v>
       </c>
-      <c r="B49" s="22">
+      <c r="B49" s="23">
         <v>-6.58</v>
       </c>
-      <c r="C49" s="22">
+      <c r="C49" s="23">
         <v>-37.61</v>
       </c>
-      <c r="D49" s="22">
+      <c r="D49" s="23">
         <v>-4.69</v>
       </c>
-      <c r="E49" s="22">
+      <c r="E49" s="23">
         <v>-7.98</v>
       </c>
-      <c r="F49" s="22">
+      <c r="F49" s="23">
         <v>-1.2</v>
       </c>
-      <c r="G49" s="22">
+      <c r="G49" s="23">
         <v>-4.03</v>
       </c>
-      <c r="H49" s="22">
+      <c r="H49" s="23">
         <v>-11.35</v>
       </c>
-      <c r="I49" s="22">
+      <c r="I49" s="23">
         <v>-8.59</v>
       </c>
-      <c r="J49" s="22">
+      <c r="J49" s="23">
         <v>-2.91</v>
       </c>
-      <c r="K49" s="22">
+      <c r="K49" s="23">
         <v>-3.37</v>
       </c>
-      <c r="L49" s="22">
+      <c r="L49" s="23">
         <v>-13.28</v>
       </c>
-      <c r="M49" s="22">
+      <c r="M49" s="23">
         <v>-1.88</v>
       </c>
-      <c r="N49" s="22">
+      <c r="N49" s="23">
         <v>-0.81</v>
       </c>
-      <c r="O49" s="22">
+      <c r="O49" s="23">
         <v>-0.59</v>
       </c>
-      <c r="P49" s="22">
+      <c r="P49" s="23">
         <v>-2.19</v>
       </c>
-      <c r="Q49" s="22">
+      <c r="Q49" s="23">
         <v>-2.58</v>
       </c>
-      <c r="R49" s="22">
+      <c r="R49" s="23">
         <v>-6.05</v>
       </c>
     </row>
@@ -12871,55 +12874,55 @@
       <c r="A50" s="14" t="s">
         <v>241</v>
       </c>
-      <c r="B50" s="21">
+      <c r="B50" s="22">
         <v>-1.49</v>
       </c>
-      <c r="C50" s="21">
+      <c r="C50" s="22">
         <v>-1.35</v>
       </c>
-      <c r="D50" s="21">
+      <c r="D50" s="22">
         <v>-1.32</v>
       </c>
-      <c r="E50" s="21">
+      <c r="E50" s="22">
         <v>-1.34</v>
       </c>
-      <c r="F50" s="21">
+      <c r="F50" s="22">
         <v>-1.4</v>
       </c>
-      <c r="G50" s="21">
+      <c r="G50" s="22">
         <v>-1.42</v>
       </c>
-      <c r="H50" s="21">
+      <c r="H50" s="22">
         <v>-1.33</v>
       </c>
-      <c r="I50" s="21">
+      <c r="I50" s="22">
         <v>-1.3</v>
       </c>
-      <c r="J50" s="21">
+      <c r="J50" s="22">
         <v>-1.23</v>
       </c>
-      <c r="K50" s="21">
+      <c r="K50" s="22">
         <v>-1.25</v>
       </c>
-      <c r="L50" s="21">
+      <c r="L50" s="22">
         <v>-1.02</v>
       </c>
-      <c r="M50" s="21">
+      <c r="M50" s="22">
         <v>-0.57</v>
       </c>
-      <c r="N50" s="21">
+      <c r="N50" s="22">
         <v>-0.16</v>
       </c>
-      <c r="O50" s="21">
+      <c r="O50" s="22">
         <v>-0.39</v>
       </c>
-      <c r="P50" s="21">
+      <c r="P50" s="22">
         <v>-0.38</v>
       </c>
-      <c r="Q50" s="21">
+      <c r="Q50" s="22">
         <v>-0.38</v>
       </c>
-      <c r="R50" s="21">
+      <c r="R50" s="22">
         <v>-0.39</v>
       </c>
     </row>
@@ -12953,55 +12956,55 @@
       <c r="A52" s="14" t="s">
         <v>243</v>
       </c>
-      <c r="B52" s="21">
+      <c r="B52" s="22">
         <v>-8.59</v>
       </c>
-      <c r="C52" s="21">
+      <c r="C52" s="22">
         <v>-10.11</v>
       </c>
-      <c r="D52" s="21">
+      <c r="D52" s="22">
         <v>-6.68</v>
       </c>
-      <c r="E52" s="21">
+      <c r="E52" s="22">
         <v>-26.56</v>
       </c>
-      <c r="F52" s="21">
+      <c r="F52" s="22">
         <v>-6.68</v>
       </c>
-      <c r="G52" s="21">
+      <c r="G52" s="22">
         <v>-6.59</v>
       </c>
-      <c r="H52" s="21">
+      <c r="H52" s="22">
         <v>-5.62</v>
       </c>
-      <c r="I52" s="21">
+      <c r="I52" s="22">
         <v>-5.55</v>
       </c>
-      <c r="J52" s="21">
+      <c r="J52" s="22">
         <v>-5.32</v>
       </c>
-      <c r="K52" s="21">
+      <c r="K52" s="22">
         <v>-5.41</v>
       </c>
-      <c r="L52" s="21">
+      <c r="L52" s="22">
         <v>-4.46</v>
       </c>
-      <c r="M52" s="21">
+      <c r="M52" s="22">
         <v>-4.55</v>
       </c>
-      <c r="N52" s="21">
+      <c r="N52" s="22">
         <v>-5.43</v>
       </c>
-      <c r="O52" s="21">
+      <c r="O52" s="22">
         <v>-5.47</v>
       </c>
-      <c r="P52" s="21">
+      <c r="P52" s="22">
         <v>-18.8</v>
       </c>
       <c r="Q52" s="15">
         <v>0.0</v>
       </c>
-      <c r="R52" s="21">
+      <c r="R52" s="22">
         <v>-6.67</v>
       </c>
     </row>
@@ -13025,13 +13028,13 @@
       <c r="M53" s="15">
         <v>0.0</v>
       </c>
-      <c r="N53" s="21">
+      <c r="N53" s="22">
         <v>-0.38</v>
       </c>
-      <c r="O53" s="21">
+      <c r="O53" s="22">
         <v>-0.23</v>
       </c>
-      <c r="P53" s="21">
+      <c r="P53" s="22">
         <v>-0.02</v>
       </c>
       <c r="Q53" s="15"/>
@@ -13041,22 +13044,22 @@
       <c r="A54" s="14" t="s">
         <v>245</v>
       </c>
-      <c r="B54" s="21">
+      <c r="B54" s="22">
         <v>-10.14</v>
       </c>
-      <c r="C54" s="21">
+      <c r="C54" s="22">
         <v>-9.82</v>
       </c>
-      <c r="D54" s="21">
+      <c r="D54" s="22">
         <v>-3.55</v>
       </c>
-      <c r="E54" s="21">
+      <c r="E54" s="22">
         <v>-2.0</v>
       </c>
-      <c r="F54" s="21">
+      <c r="F54" s="22">
         <v>-1.27</v>
       </c>
-      <c r="G54" s="21">
+      <c r="G54" s="22">
         <v>-1.8</v>
       </c>
       <c r="H54" s="15"/>
@@ -13101,7 +13104,7 @@
       <c r="A56" s="14" t="s">
         <v>247</v>
       </c>
-      <c r="B56" s="21">
+      <c r="B56" s="22">
         <v>-11.17</v>
       </c>
       <c r="C56" s="15"/>
@@ -13149,55 +13152,55 @@
       <c r="A58" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="B58" s="22">
+      <c r="B58" s="23">
         <v>-31.37</v>
       </c>
-      <c r="C58" s="22">
+      <c r="C58" s="23">
         <v>-5.79</v>
       </c>
-      <c r="D58" s="22">
+      <c r="D58" s="23">
         <v>-11.54</v>
       </c>
-      <c r="E58" s="22">
+      <c r="E58" s="23">
         <v>-29.89</v>
       </c>
-      <c r="F58" s="22">
+      <c r="F58" s="23">
         <v>-9.34</v>
       </c>
-      <c r="G58" s="22">
+      <c r="G58" s="23">
         <v>-9.81</v>
       </c>
-      <c r="H58" s="22">
+      <c r="H58" s="23">
         <v>-6.95</v>
       </c>
-      <c r="I58" s="22">
+      <c r="I58" s="23">
         <v>-6.85</v>
       </c>
-      <c r="J58" s="22">
+      <c r="J58" s="23">
         <v>-6.55</v>
       </c>
-      <c r="K58" s="22">
+      <c r="K58" s="23">
         <v>-6.66</v>
       </c>
       <c r="L58" s="20">
         <v>5.37</v>
       </c>
-      <c r="M58" s="22">
+      <c r="M58" s="23">
         <v>-5.12</v>
       </c>
-      <c r="N58" s="22">
+      <c r="N58" s="23">
         <v>-5.96</v>
       </c>
-      <c r="O58" s="22">
+      <c r="O58" s="23">
         <v>-6.09</v>
       </c>
-      <c r="P58" s="22">
+      <c r="P58" s="23">
         <v>-19.2</v>
       </c>
-      <c r="Q58" s="22">
+      <c r="Q58" s="23">
         <v>-0.38</v>
       </c>
-      <c r="R58" s="22">
+      <c r="R58" s="23">
         <v>-7.07</v>
       </c>
     </row>
@@ -13317,13 +13320,13 @@
       <c r="A61" s="14" t="s">
         <v>252</v>
       </c>
-      <c r="B61" s="21">
+      <c r="B61" s="22">
         <v>-0.29</v>
       </c>
-      <c r="C61" s="21">
+      <c r="C61" s="22">
         <v>-0.2</v>
       </c>
-      <c r="D61" s="21">
+      <c r="D61" s="22">
         <v>-0.46</v>
       </c>
       <c r="E61" s="15">
@@ -13335,13 +13338,13 @@
       <c r="G61" s="17">
         <v>0.02</v>
       </c>
-      <c r="H61" s="21">
+      <c r="H61" s="22">
         <v>-0.1</v>
       </c>
       <c r="I61" s="17">
         <v>0.03</v>
       </c>
-      <c r="J61" s="21">
+      <c r="J61" s="22">
         <v>-0.04</v>
       </c>
       <c r="K61" s="17">
@@ -13364,13 +13367,13 @@
       <c r="B62" s="17">
         <v>3.99</v>
       </c>
-      <c r="C62" s="21">
+      <c r="C62" s="22">
         <v>-3.72</v>
       </c>
       <c r="D62" s="17">
         <v>5.77</v>
       </c>
-      <c r="E62" s="21">
+      <c r="E62" s="22">
         <v>-36.15</v>
       </c>
       <c r="F62" s="17">
@@ -13379,7 +13382,7 @@
       <c r="G62" s="17">
         <v>17.42</v>
       </c>
-      <c r="H62" s="21">
+      <c r="H62" s="22">
         <v>-16.67</v>
       </c>
       <c r="I62" s="17">
@@ -13388,10 +13391,10 @@
       <c r="J62" s="17">
         <v>8.22</v>
       </c>
-      <c r="K62" s="21">
+      <c r="K62" s="22">
         <v>-1.51</v>
       </c>
-      <c r="L62" s="21">
+      <c r="L62" s="22">
         <v>-5.3</v>
       </c>
       <c r="M62" s="15"/>
@@ -13432,13 +13435,13 @@
       <c r="B64" s="20">
         <v>3.71</v>
       </c>
-      <c r="C64" s="22">
+      <c r="C64" s="23">
         <v>-3.92</v>
       </c>
       <c r="D64" s="20">
         <v>5.31</v>
       </c>
-      <c r="E64" s="22">
+      <c r="E64" s="23">
         <v>-36.15</v>
       </c>
       <c r="F64" s="20">
@@ -13447,7 +13450,7 @@
       <c r="G64" s="20">
         <v>17.44</v>
       </c>
-      <c r="H64" s="22">
+      <c r="H64" s="23">
         <v>-16.78</v>
       </c>
       <c r="I64" s="20">
@@ -13456,10 +13459,10 @@
       <c r="J64" s="20">
         <v>8.18</v>
       </c>
-      <c r="K64" s="22">
+      <c r="K64" s="23">
         <v>-1.48</v>
       </c>
-      <c r="L64" s="22">
+      <c r="L64" s="23">
         <v>-5.27</v>
       </c>
       <c r="M64" s="20">
@@ -13468,10 +13471,10 @@
       <c r="N64" s="20">
         <v>6.29</v>
       </c>
-      <c r="O64" s="22">
+      <c r="O64" s="23">
         <v>-1.02</v>
       </c>
-      <c r="P64" s="22">
+      <c r="P64" s="23">
         <v>-20.82</v>
       </c>
       <c r="Q64" s="20">
@@ -15198,3569 +15201,3569 @@
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="25" t="s">
+      <c r="A20" s="26" t="s">
         <v>280</v>
       </c>
-      <c r="B20" s="26"/>
-      <c r="C20" s="26"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
-      <c r="I20" s="26"/>
-      <c r="J20" s="26"/>
-      <c r="K20" s="26"/>
-      <c r="L20" s="26"/>
-      <c r="M20" s="26"/>
-      <c r="N20" s="26"/>
-      <c r="O20" s="26"/>
-      <c r="P20" s="26"/>
-      <c r="Q20" s="26"/>
-      <c r="R20" s="26"/>
-      <c r="S20" s="26"/>
-      <c r="T20" s="26"/>
-      <c r="U20" s="26"/>
-      <c r="V20" s="26"/>
-      <c r="W20" s="26"/>
-      <c r="X20" s="26"/>
-      <c r="Y20" s="26"/>
-      <c r="Z20" s="26"/>
-      <c r="AA20" s="26"/>
-      <c r="AB20" s="26"/>
-      <c r="AC20" s="26"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="27"/>
+      <c r="J20" s="27"/>
+      <c r="K20" s="27"/>
+      <c r="L20" s="27"/>
+      <c r="M20" s="27"/>
+      <c r="N20" s="27"/>
+      <c r="O20" s="27"/>
+      <c r="P20" s="27"/>
+      <c r="Q20" s="27"/>
+      <c r="R20" s="27"/>
+      <c r="S20" s="27"/>
+      <c r="T20" s="27"/>
+      <c r="U20" s="27"/>
+      <c r="V20" s="27"/>
+      <c r="W20" s="27"/>
+      <c r="X20" s="27"/>
+      <c r="Y20" s="27"/>
+      <c r="Z20" s="27"/>
+      <c r="AA20" s="27"/>
+      <c r="AB20" s="27"/>
+      <c r="AC20" s="27"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="27" t="s">
+      <c r="A21" s="28" t="s">
         <v>280</v>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="29">
         <v>287.34</v>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="29">
         <v>304.86</v>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="29">
         <v>190.88</v>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="29">
         <v>200.66</v>
       </c>
-      <c r="F21" s="28">
+      <c r="F21" s="29">
         <v>119.28</v>
       </c>
-      <c r="G21" s="28">
+      <c r="G21" s="29">
         <v>111.05</v>
       </c>
-      <c r="H21" s="28">
+      <c r="H21" s="29">
         <v>116.97</v>
       </c>
-      <c r="I21" s="28">
+      <c r="I21" s="29">
         <v>111.65</v>
       </c>
-      <c r="J21" s="28">
+      <c r="J21" s="29">
         <v>104.88</v>
       </c>
-      <c r="K21" s="28">
+      <c r="K21" s="29">
         <v>113.18</v>
       </c>
-      <c r="L21" s="28">
+      <c r="L21" s="29">
         <v>120.21</v>
       </c>
-      <c r="M21" s="29">
+      <c r="M21" s="30">
         <v>66.51</v>
       </c>
-      <c r="N21" s="29">
+      <c r="N21" s="30">
         <v>62.99</v>
       </c>
-      <c r="O21" s="29">
+      <c r="O21" s="30">
         <v>58.82</v>
       </c>
-      <c r="P21" s="29">
+      <c r="P21" s="30">
         <v>61.76</v>
       </c>
-      <c r="Q21" s="29">
+      <c r="Q21" s="30">
         <v>12.58</v>
       </c>
-      <c r="R21" s="29">
+      <c r="R21" s="30">
         <v>39.77</v>
       </c>
-      <c r="S21" s="29">
+      <c r="S21" s="30">
         <v>62.38</v>
       </c>
-      <c r="T21" s="29">
+      <c r="T21" s="30">
         <v>69.5</v>
       </c>
-      <c r="U21" s="29">
+      <c r="U21" s="30">
         <v>79.99</v>
       </c>
-      <c r="V21" s="29">
+      <c r="V21" s="30">
         <v>50.86</v>
       </c>
-      <c r="W21" s="29">
+      <c r="W21" s="30">
         <v>15.03</v>
       </c>
-      <c r="X21" s="29">
+      <c r="X21" s="30">
         <v>17.3</v>
       </c>
-      <c r="Y21" s="29">
+      <c r="Y21" s="30">
         <v>18.14</v>
       </c>
-      <c r="Z21" s="29">
+      <c r="Z21" s="30">
         <v>18.29</v>
       </c>
-      <c r="AA21" s="29">
+      <c r="AA21" s="30">
         <v>15.13</v>
       </c>
-      <c r="AB21" s="29">
+      <c r="AB21" s="30">
         <v>50.88</v>
       </c>
-      <c r="AC21" s="29">
+      <c r="AC21" s="30">
         <v>59.87</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="27" t="s">
+      <c r="A22" s="28" t="s">
         <v>281</v>
       </c>
-      <c r="B22" s="28">
+      <c r="B22" s="29">
         <v>229.16</v>
       </c>
-      <c r="C22" s="28">
+      <c r="C22" s="29">
         <v>196.13</v>
       </c>
-      <c r="D22" s="28">
+      <c r="D22" s="29">
         <v>156.68</v>
       </c>
-      <c r="E22" s="28">
+      <c r="E22" s="29">
         <v>137.53</v>
       </c>
-      <c r="F22" s="28">
+      <c r="F22" s="29">
         <v>115.03</v>
       </c>
-      <c r="G22" s="28">
+      <c r="G22" s="29">
         <v>125.94</v>
       </c>
-      <c r="H22" s="28">
+      <c r="H22" s="29">
         <v>118.77</v>
       </c>
-      <c r="I22" s="28">
+      <c r="I22" s="29">
         <v>106.52</v>
       </c>
-      <c r="J22" s="29">
+      <c r="J22" s="30">
         <v>98.55</v>
       </c>
-      <c r="K22" s="29">
+      <c r="K22" s="30">
         <v>88.37</v>
       </c>
-      <c r="L22" s="29">
+      <c r="L22" s="30">
         <v>84.47</v>
       </c>
-      <c r="M22" s="29">
+      <c r="M22" s="30">
         <v>54.2</v>
       </c>
-      <c r="N22" s="29">
+      <c r="N22" s="30">
         <v>48.56</v>
       </c>
-      <c r="O22" s="29">
+      <c r="O22" s="30">
         <v>43.66</v>
       </c>
-      <c r="P22" s="29">
+      <c r="P22" s="30">
         <v>48.33</v>
       </c>
-      <c r="Q22" s="29">
+      <c r="Q22" s="30">
         <v>52.06</v>
       </c>
-      <c r="R22" s="29">
+      <c r="R22" s="30">
         <v>63.3</v>
       </c>
-      <c r="S22" s="29">
+      <c r="S22" s="30">
         <v>57.03</v>
       </c>
-      <c r="T22" s="29">
+      <c r="T22" s="30">
         <v>44.68</v>
       </c>
-      <c r="U22" s="29">
+      <c r="U22" s="30">
         <v>37.29</v>
       </c>
-      <c r="V22" s="29">
+      <c r="V22" s="30">
         <v>23.75</v>
       </c>
-      <c r="W22" s="29">
+      <c r="W22" s="30">
         <v>17.55</v>
       </c>
-      <c r="X22" s="29">
+      <c r="X22" s="30">
         <v>24.61</v>
       </c>
-      <c r="Y22" s="29">
+      <c r="Y22" s="30">
         <v>28.91</v>
       </c>
-      <c r="Z22" s="30"/>
-      <c r="AA22" s="30"/>
-      <c r="AB22" s="30"/>
-      <c r="AC22" s="30"/>
+      <c r="Z22" s="31"/>
+      <c r="AA22" s="31"/>
+      <c r="AB22" s="31"/>
+      <c r="AC22" s="31"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="25" t="s">
+      <c r="A23" s="26" t="s">
         <v>282</v>
       </c>
-      <c r="B23" s="26"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="26"/>
-      <c r="K23" s="26"/>
-      <c r="L23" s="26"/>
-      <c r="M23" s="26"/>
-      <c r="N23" s="26"/>
-      <c r="O23" s="26"/>
-      <c r="P23" s="26"/>
-      <c r="Q23" s="26"/>
-      <c r="R23" s="26"/>
-      <c r="S23" s="26"/>
-      <c r="T23" s="26"/>
-      <c r="U23" s="26"/>
-      <c r="V23" s="26"/>
-      <c r="W23" s="26"/>
-      <c r="X23" s="26"/>
-      <c r="Y23" s="26"/>
-      <c r="Z23" s="26"/>
-      <c r="AA23" s="26"/>
-      <c r="AB23" s="26"/>
-      <c r="AC23" s="26"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="27"/>
+      <c r="K23" s="27"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="27"/>
+      <c r="N23" s="27"/>
+      <c r="O23" s="27"/>
+      <c r="P23" s="27"/>
+      <c r="Q23" s="27"/>
+      <c r="R23" s="27"/>
+      <c r="S23" s="27"/>
+      <c r="T23" s="27"/>
+      <c r="U23" s="27"/>
+      <c r="V23" s="27"/>
+      <c r="W23" s="27"/>
+      <c r="X23" s="27"/>
+      <c r="Y23" s="27"/>
+      <c r="Z23" s="27"/>
+      <c r="AA23" s="27"/>
+      <c r="AB23" s="27"/>
+      <c r="AC23" s="27"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="27" t="s">
+      <c r="A24" s="28" t="s">
         <v>282</v>
       </c>
-      <c r="B24" s="28">
+      <c r="B24" s="29">
         <v>207.61</v>
       </c>
-      <c r="C24" s="28">
+      <c r="C24" s="29">
         <v>207.32</v>
       </c>
-      <c r="D24" s="28">
+      <c r="D24" s="29">
         <v>175.34</v>
       </c>
-      <c r="E24" s="28">
+      <c r="E24" s="29">
         <v>185.07</v>
       </c>
-      <c r="F24" s="28">
+      <c r="F24" s="29">
         <v>147.7</v>
       </c>
-      <c r="G24" s="28">
+      <c r="G24" s="29">
         <v>116.6</v>
       </c>
-      <c r="H24" s="28">
+      <c r="H24" s="29">
         <v>108.89</v>
       </c>
-      <c r="I24" s="28">
+      <c r="I24" s="29">
         <v>120.71</v>
       </c>
-      <c r="J24" s="28">
+      <c r="J24" s="29">
         <v>108.66</v>
       </c>
-      <c r="K24" s="28">
+      <c r="K24" s="29">
         <v>107.6</v>
       </c>
-      <c r="L24" s="28">
+      <c r="L24" s="29">
         <v>114.56</v>
       </c>
-      <c r="M24" s="29">
+      <c r="M24" s="30">
         <v>75.69</v>
       </c>
-      <c r="N24" s="29">
+      <c r="N24" s="30">
         <v>66.68</v>
       </c>
-      <c r="O24" s="29">
+      <c r="O24" s="30">
         <v>55.91</v>
       </c>
-      <c r="P24" s="29">
+      <c r="P24" s="30">
         <v>59.3</v>
       </c>
-      <c r="Q24" s="29">
+      <c r="Q24" s="30">
         <v>30.87</v>
       </c>
-      <c r="R24" s="29">
+      <c r="R24" s="30">
         <v>46.13</v>
       </c>
-      <c r="S24" s="29">
+      <c r="S24" s="30">
         <v>62.41</v>
       </c>
-      <c r="T24" s="29">
+      <c r="T24" s="30">
         <v>65.64</v>
       </c>
-      <c r="U24" s="29">
+      <c r="U24" s="30">
         <v>77.16</v>
       </c>
-      <c r="V24" s="29">
+      <c r="V24" s="30">
         <v>55.42</v>
       </c>
-      <c r="W24" s="29">
+      <c r="W24" s="30">
         <v>26.98</v>
       </c>
-      <c r="X24" s="29">
+      <c r="X24" s="30">
         <v>22.3</v>
       </c>
-      <c r="Y24" s="29">
+      <c r="Y24" s="30">
         <v>19.17</v>
       </c>
-      <c r="Z24" s="29">
+      <c r="Z24" s="30">
         <v>35.02</v>
       </c>
-      <c r="AA24" s="29">
+      <c r="AA24" s="30">
         <v>41.3</v>
       </c>
-      <c r="AB24" s="29">
+      <c r="AB24" s="30">
         <v>45.03</v>
       </c>
-      <c r="AC24" s="29">
+      <c r="AC24" s="30">
         <v>56.25</v>
       </c>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="27" t="s">
+      <c r="A25" s="28" t="s">
         <v>283</v>
       </c>
-      <c r="B25" s="28">
+      <c r="B25" s="29">
         <v>193.7</v>
       </c>
-      <c r="C25" s="28">
+      <c r="C25" s="29">
         <v>177.73</v>
       </c>
-      <c r="D25" s="28">
+      <c r="D25" s="29">
         <v>155.91</v>
       </c>
-      <c r="E25" s="28">
+      <c r="E25" s="29">
         <v>141.79</v>
       </c>
-      <c r="F25" s="28">
+      <c r="F25" s="29">
         <v>122.84</v>
       </c>
-      <c r="G25" s="28">
+      <c r="G25" s="29">
         <v>126.89</v>
       </c>
-      <c r="H25" s="28">
+      <c r="H25" s="29">
         <v>117.45</v>
       </c>
-      <c r="I25" s="28">
+      <c r="I25" s="29">
         <v>108.93</v>
       </c>
-      <c r="J25" s="28">
+      <c r="J25" s="29">
         <v>100.0</v>
       </c>
-      <c r="K25" s="29">
+      <c r="K25" s="30">
         <v>88.32</v>
       </c>
-      <c r="L25" s="29">
+      <c r="L25" s="30">
         <v>85.01</v>
       </c>
-      <c r="M25" s="29">
+      <c r="M25" s="30">
         <v>59.33</v>
       </c>
-      <c r="N25" s="29">
+      <c r="N25" s="30">
         <v>53.08</v>
       </c>
-      <c r="O25" s="29">
+      <c r="O25" s="30">
         <v>47.09</v>
       </c>
-      <c r="P25" s="29">
+      <c r="P25" s="30">
         <v>51.83</v>
       </c>
-      <c r="Q25" s="29">
+      <c r="Q25" s="30">
         <v>55.57</v>
       </c>
-      <c r="R25" s="29">
+      <c r="R25" s="30">
         <v>64.13</v>
       </c>
-      <c r="S25" s="29">
+      <c r="S25" s="30">
         <v>58.97</v>
       </c>
-      <c r="T25" s="29">
+      <c r="T25" s="30">
         <v>47.41</v>
       </c>
-      <c r="U25" s="29">
+      <c r="U25" s="30">
         <v>41.3</v>
       </c>
-      <c r="V25" s="29">
+      <c r="V25" s="30">
         <v>31.33</v>
       </c>
-      <c r="W25" s="29">
+      <c r="W25" s="30">
         <v>30.08</v>
       </c>
-      <c r="X25" s="29">
+      <c r="X25" s="30">
         <v>33.47</v>
       </c>
-      <c r="Y25" s="29">
+      <c r="Y25" s="30">
         <v>35.28</v>
       </c>
-      <c r="Z25" s="30"/>
-      <c r="AA25" s="30"/>
-      <c r="AB25" s="30"/>
-      <c r="AC25" s="30"/>
+      <c r="Z25" s="31"/>
+      <c r="AA25" s="31"/>
+      <c r="AB25" s="31"/>
+      <c r="AC25" s="31"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="25" t="s">
+      <c r="A26" s="26" t="s">
         <v>284</v>
       </c>
-      <c r="B26" s="26"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="26"/>
-      <c r="J26" s="26"/>
-      <c r="K26" s="26"/>
-      <c r="L26" s="26"/>
-      <c r="M26" s="26"/>
-      <c r="N26" s="26"/>
-      <c r="O26" s="26"/>
-      <c r="P26" s="26"/>
-      <c r="Q26" s="26"/>
-      <c r="R26" s="26"/>
-      <c r="S26" s="26"/>
-      <c r="T26" s="26"/>
-      <c r="U26" s="26"/>
-      <c r="V26" s="26"/>
-      <c r="W26" s="26"/>
-      <c r="X26" s="26"/>
-      <c r="Y26" s="26"/>
-      <c r="Z26" s="26"/>
-      <c r="AA26" s="26"/>
-      <c r="AB26" s="26"/>
-      <c r="AC26" s="26"/>
+      <c r="B26" s="27"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27"/>
+      <c r="I26" s="27"/>
+      <c r="J26" s="27"/>
+      <c r="K26" s="27"/>
+      <c r="L26" s="27"/>
+      <c r="M26" s="27"/>
+      <c r="N26" s="27"/>
+      <c r="O26" s="27"/>
+      <c r="P26" s="27"/>
+      <c r="Q26" s="27"/>
+      <c r="R26" s="27"/>
+      <c r="S26" s="27"/>
+      <c r="T26" s="27"/>
+      <c r="U26" s="27"/>
+      <c r="V26" s="27"/>
+      <c r="W26" s="27"/>
+      <c r="X26" s="27"/>
+      <c r="Y26" s="27"/>
+      <c r="Z26" s="27"/>
+      <c r="AA26" s="27"/>
+      <c r="AB26" s="27"/>
+      <c r="AC26" s="27"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="27" t="s">
+      <c r="A27" s="28" t="s">
         <v>285</v>
       </c>
-      <c r="B27" s="28">
+      <c r="B27" s="29">
         <v>6277.77</v>
       </c>
-      <c r="C27" s="28">
+      <c r="C27" s="29">
         <v>6269.0</v>
       </c>
-      <c r="D27" s="28">
+      <c r="D27" s="29">
         <v>5302.21</v>
       </c>
-      <c r="E27" s="28">
+      <c r="E27" s="29">
         <v>5596.16</v>
       </c>
-      <c r="F27" s="28">
+      <c r="F27" s="29">
         <v>4466.25</v>
       </c>
-      <c r="G27" s="28">
+      <c r="G27" s="29">
         <v>3525.74</v>
       </c>
-      <c r="H27" s="28">
+      <c r="H27" s="29">
         <v>3292.58</v>
       </c>
-      <c r="I27" s="28">
+      <c r="I27" s="29">
         <v>3650.16</v>
       </c>
-      <c r="J27" s="28">
+      <c r="J27" s="29">
         <v>3285.76</v>
       </c>
-      <c r="K27" s="28">
+      <c r="K27" s="29">
         <v>3253.8</v>
       </c>
-      <c r="L27" s="28">
+      <c r="L27" s="29">
         <v>3464.17</v>
       </c>
-      <c r="M27" s="28">
+      <c r="M27" s="29">
         <v>2288.92</v>
       </c>
-      <c r="N27" s="28">
+      <c r="N27" s="29">
         <v>2017.46</v>
       </c>
-      <c r="O27" s="28">
+      <c r="O27" s="29">
         <v>1691.67</v>
       </c>
-      <c r="P27" s="28">
+      <c r="P27" s="29">
         <v>1794.17</v>
       </c>
-      <c r="Q27" s="28">
+      <c r="Q27" s="29">
         <v>934.19</v>
       </c>
-      <c r="R27" s="28">
+      <c r="R27" s="29">
         <v>1395.7</v>
       </c>
-      <c r="S27" s="28">
+      <c r="S27" s="29">
         <v>1888.31</v>
       </c>
-      <c r="T27" s="28">
+      <c r="T27" s="29">
         <v>1986.1</v>
       </c>
-      <c r="U27" s="28">
+      <c r="U27" s="29">
         <v>2334.75</v>
       </c>
-      <c r="V27" s="28">
+      <c r="V27" s="29">
         <v>1676.76</v>
       </c>
-      <c r="W27" s="28">
+      <c r="W27" s="29">
         <v>816.4</v>
       </c>
-      <c r="X27" s="28">
+      <c r="X27" s="29">
         <v>674.8</v>
       </c>
-      <c r="Y27" s="28">
+      <c r="Y27" s="29">
         <v>580.17</v>
       </c>
-      <c r="Z27" s="28">
+      <c r="Z27" s="29">
         <v>905.56</v>
       </c>
-      <c r="AA27" s="28">
+      <c r="AA27" s="29">
         <v>809.75</v>
       </c>
-      <c r="AB27" s="28">
+      <c r="AB27" s="29">
         <v>804.13</v>
       </c>
-      <c r="AC27" s="28">
+      <c r="AC27" s="29">
         <v>803.5</v>
       </c>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="27" t="s">
+      <c r="A28" s="28" t="s">
         <v>286</v>
       </c>
-      <c r="B28" s="28">
+      <c r="B28" s="29">
         <v>5857.16</v>
       </c>
-      <c r="C28" s="28">
+      <c r="C28" s="29">
         <v>5374.33</v>
       </c>
-      <c r="D28" s="28">
+      <c r="D28" s="29">
         <v>4714.43</v>
       </c>
-      <c r="E28" s="28">
+      <c r="E28" s="29">
         <v>4287.52</v>
       </c>
-      <c r="F28" s="28">
+      <c r="F28" s="29">
         <v>3714.61</v>
       </c>
-      <c r="G28" s="28">
+      <c r="G28" s="29">
         <v>3836.89</v>
       </c>
-      <c r="H28" s="28">
+      <c r="H28" s="29">
         <v>3551.47</v>
       </c>
-      <c r="I28" s="28">
+      <c r="I28" s="29">
         <v>3294.02</v>
       </c>
-      <c r="J28" s="28">
+      <c r="J28" s="29">
         <v>3024.16</v>
       </c>
-      <c r="K28" s="28">
+      <c r="K28" s="29">
         <v>2671.27</v>
       </c>
-      <c r="L28" s="28">
+      <c r="L28" s="29">
         <v>2571.35</v>
       </c>
-      <c r="M28" s="28">
+      <c r="M28" s="29">
         <v>1794.95</v>
       </c>
-      <c r="N28" s="28">
+      <c r="N28" s="29">
         <v>1606.12</v>
       </c>
-      <c r="O28" s="28">
+      <c r="O28" s="29">
         <v>1424.79</v>
       </c>
-      <c r="P28" s="28">
+      <c r="P28" s="29">
         <v>1568.31</v>
       </c>
-      <c r="Q28" s="28">
+      <c r="Q28" s="29">
         <v>1681.54</v>
       </c>
-      <c r="R28" s="28">
+      <c r="R28" s="29">
         <v>1940.37</v>
       </c>
-      <c r="S28" s="28">
+      <c r="S28" s="29">
         <v>1784.15</v>
       </c>
-      <c r="T28" s="28">
+      <c r="T28" s="29">
         <v>1434.61</v>
       </c>
-      <c r="U28" s="28">
+      <c r="U28" s="29">
         <v>1249.65</v>
       </c>
-      <c r="V28" s="28">
+      <c r="V28" s="29">
         <v>918.11</v>
       </c>
-      <c r="W28" s="28">
+      <c r="W28" s="29">
         <v>786.87</v>
       </c>
-      <c r="X28" s="28">
+      <c r="X28" s="29">
         <v>778.35</v>
       </c>
-      <c r="Y28" s="28">
+      <c r="Y28" s="29">
         <v>707.61</v>
       </c>
-      <c r="Z28" s="30"/>
-      <c r="AA28" s="30"/>
-      <c r="AB28" s="30"/>
-      <c r="AC28" s="30"/>
+      <c r="Z28" s="31"/>
+      <c r="AA28" s="31"/>
+      <c r="AB28" s="31"/>
+      <c r="AC28" s="31"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="25" t="s">
+      <c r="A29" s="26" t="s">
         <v>287</v>
       </c>
-      <c r="B29" s="26"/>
-      <c r="C29" s="26"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="26"/>
-      <c r="I29" s="26"/>
-      <c r="J29" s="26"/>
-      <c r="K29" s="26"/>
-      <c r="L29" s="26"/>
-      <c r="M29" s="26"/>
-      <c r="N29" s="26"/>
-      <c r="O29" s="26"/>
-      <c r="P29" s="26"/>
-      <c r="Q29" s="26"/>
-      <c r="R29" s="26"/>
-      <c r="S29" s="26"/>
-      <c r="T29" s="26"/>
-      <c r="U29" s="26"/>
-      <c r="V29" s="26"/>
-      <c r="W29" s="26"/>
-      <c r="X29" s="26"/>
-      <c r="Y29" s="26"/>
-      <c r="Z29" s="26"/>
-      <c r="AA29" s="26"/>
-      <c r="AB29" s="26"/>
-      <c r="AC29" s="26"/>
+      <c r="B29" s="27"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="27"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="27"/>
+      <c r="I29" s="27"/>
+      <c r="J29" s="27"/>
+      <c r="K29" s="27"/>
+      <c r="L29" s="27"/>
+      <c r="M29" s="27"/>
+      <c r="N29" s="27"/>
+      <c r="O29" s="27"/>
+      <c r="P29" s="27"/>
+      <c r="Q29" s="27"/>
+      <c r="R29" s="27"/>
+      <c r="S29" s="27"/>
+      <c r="T29" s="27"/>
+      <c r="U29" s="27"/>
+      <c r="V29" s="27"/>
+      <c r="W29" s="27"/>
+      <c r="X29" s="27"/>
+      <c r="Y29" s="27"/>
+      <c r="Z29" s="27"/>
+      <c r="AA29" s="27"/>
+      <c r="AB29" s="27"/>
+      <c r="AC29" s="27"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="27" t="s">
+      <c r="A30" s="28" t="s">
         <v>288</v>
       </c>
-      <c r="B30" s="31">
+      <c r="B30" s="32">
         <v>11.14</v>
       </c>
-      <c r="C30" s="31">
+      <c r="C30" s="32">
         <v>11.37</v>
       </c>
-      <c r="D30" s="31">
+      <c r="D30" s="32">
         <v>6.57</v>
       </c>
-      <c r="E30" s="32">
+      <c r="E30" s="33">
         <v>-0.87</v>
       </c>
-      <c r="F30" s="31">
+      <c r="F30" s="32">
         <v>13.53</v>
       </c>
-      <c r="G30" s="31">
+      <c r="G30" s="32">
         <v>15.72</v>
       </c>
-      <c r="H30" s="32">
+      <c r="H30" s="33">
         <v>-3.94</v>
       </c>
-      <c r="I30" s="31">
+      <c r="I30" s="32">
         <v>5.8</v>
       </c>
-      <c r="J30" s="31">
+      <c r="J30" s="32">
         <v>9.06</v>
       </c>
-      <c r="K30" s="31">
+      <c r="K30" s="32">
         <v>3.0</v>
       </c>
-      <c r="L30" s="32">
+      <c r="L30" s="33">
         <v>-6.73</v>
       </c>
-      <c r="M30" s="31">
+      <c r="M30" s="32">
         <v>8.61</v>
       </c>
-      <c r="N30" s="31">
+      <c r="N30" s="32">
         <v>12.55</v>
       </c>
-      <c r="O30" s="31">
+      <c r="O30" s="32">
         <v>6.98</v>
       </c>
-      <c r="P30" s="32">
+      <c r="P30" s="33">
         <v>-1.64</v>
       </c>
-      <c r="Q30" s="31">
+      <c r="Q30" s="32">
         <v>25.36</v>
       </c>
-      <c r="R30" s="31">
+      <c r="R30" s="32">
         <v>16.84</v>
       </c>
-      <c r="S30" s="31">
+      <c r="S30" s="32">
         <v>10.15</v>
       </c>
-      <c r="T30" s="31">
+      <c r="T30" s="32">
         <v>1.68</v>
       </c>
-      <c r="U30" s="32">
+      <c r="U30" s="33">
         <v>-0.81</v>
       </c>
-      <c r="V30" s="32">
+      <c r="V30" s="33">
         <v>-2.65</v>
       </c>
-      <c r="W30" s="31">
+      <c r="W30" s="32">
         <v>22.7</v>
       </c>
-      <c r="X30" s="31">
+      <c r="X30" s="32">
         <v>9.93</v>
       </c>
-      <c r="Y30" s="31">
+      <c r="Y30" s="32">
         <v>25.93</v>
       </c>
-      <c r="Z30" s="31">
+      <c r="Z30" s="32">
         <v>0.8</v>
       </c>
-      <c r="AA30" s="31">
+      <c r="AA30" s="32">
         <v>37.44</v>
       </c>
-      <c r="AB30" s="32">
+      <c r="AB30" s="33">
         <v>-41.81</v>
       </c>
-      <c r="AC30" s="31">
+      <c r="AC30" s="32">
         <v>33.3</v>
       </c>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="27" t="s">
+      <c r="A31" s="28" t="s">
         <v>289</v>
       </c>
-      <c r="B31" s="31">
+      <c r="B31" s="32">
         <v>8.24</v>
       </c>
-      <c r="C31" s="31">
+      <c r="C31" s="32">
         <v>8.61</v>
       </c>
-      <c r="D31" s="31">
+      <c r="D31" s="32">
         <v>5.91</v>
       </c>
-      <c r="E31" s="31">
+      <c r="E31" s="32">
         <v>5.73</v>
       </c>
-      <c r="F31" s="31">
+      <c r="F31" s="32">
         <v>8.25</v>
       </c>
-      <c r="G31" s="31">
+      <c r="G31" s="32">
         <v>5.84</v>
       </c>
-      <c r="H31" s="31">
+      <c r="H31" s="32">
         <v>1.52</v>
       </c>
-      <c r="I31" s="31">
+      <c r="I31" s="32">
         <v>3.71</v>
       </c>
-      <c r="J31" s="31">
+      <c r="J31" s="32">
         <v>4.57</v>
       </c>
-      <c r="K31" s="31">
+      <c r="K31" s="32">
         <v>3.89</v>
       </c>
-      <c r="L31" s="31">
+      <c r="L31" s="32">
         <v>3.19</v>
       </c>
-      <c r="M31" s="31">
+      <c r="M31" s="32">
         <v>8.81</v>
       </c>
-      <c r="N31" s="31">
+      <c r="N31" s="32">
         <v>10.21</v>
       </c>
-      <c r="O31" s="31">
+      <c r="O31" s="32">
         <v>9.6</v>
       </c>
-      <c r="P31" s="31">
+      <c r="P31" s="32">
         <v>8.15</v>
       </c>
-      <c r="Q31" s="31">
+      <c r="Q31" s="32">
         <v>7.87</v>
       </c>
-      <c r="R31" s="31">
+      <c r="R31" s="32">
         <v>4.13</v>
       </c>
-      <c r="S31" s="31">
+      <c r="S31" s="32">
         <v>3.88</v>
       </c>
-      <c r="T31" s="31">
+      <c r="T31" s="32">
         <v>2.87</v>
       </c>
-      <c r="U31" s="31">
+      <c r="U31" s="32">
         <v>5.7</v>
       </c>
-      <c r="V31" s="31">
+      <c r="V31" s="32">
         <v>7.9</v>
       </c>
-      <c r="W31" s="31">
+      <c r="W31" s="32">
         <v>19.01</v>
       </c>
-      <c r="X31" s="31">
+      <c r="X31" s="32">
         <v>5.62</v>
       </c>
-      <c r="Y31" s="31">
+      <c r="Y31" s="32">
         <v>10.2</v>
       </c>
-      <c r="Z31" s="31"/>
-      <c r="AA31" s="31"/>
-      <c r="AB31" s="31"/>
-      <c r="AC31" s="31"/>
+      <c r="Z31" s="32"/>
+      <c r="AA31" s="32"/>
+      <c r="AB31" s="32"/>
+      <c r="AC31" s="32"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="25" t="s">
+      <c r="A32" s="26" t="s">
         <v>290</v>
       </c>
-      <c r="B32" s="26"/>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="26"/>
-      <c r="I32" s="26"/>
-      <c r="J32" s="26"/>
-      <c r="K32" s="26"/>
-      <c r="L32" s="26"/>
-      <c r="M32" s="26"/>
-      <c r="N32" s="26"/>
-      <c r="O32" s="26"/>
-      <c r="P32" s="26"/>
-      <c r="Q32" s="26"/>
-      <c r="R32" s="26"/>
-      <c r="S32" s="26"/>
-      <c r="T32" s="26"/>
-      <c r="U32" s="26"/>
-      <c r="V32" s="26"/>
-      <c r="W32" s="26"/>
-      <c r="X32" s="26"/>
-      <c r="Y32" s="26"/>
-      <c r="Z32" s="26"/>
-      <c r="AA32" s="26"/>
-      <c r="AB32" s="26"/>
-      <c r="AC32" s="26"/>
+      <c r="B32" s="27"/>
+      <c r="C32" s="27"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="27"/>
+      <c r="I32" s="27"/>
+      <c r="J32" s="27"/>
+      <c r="K32" s="27"/>
+      <c r="L32" s="27"/>
+      <c r="M32" s="27"/>
+      <c r="N32" s="27"/>
+      <c r="O32" s="27"/>
+      <c r="P32" s="27"/>
+      <c r="Q32" s="27"/>
+      <c r="R32" s="27"/>
+      <c r="S32" s="27"/>
+      <c r="T32" s="27"/>
+      <c r="U32" s="27"/>
+      <c r="V32" s="27"/>
+      <c r="W32" s="27"/>
+      <c r="X32" s="27"/>
+      <c r="Y32" s="27"/>
+      <c r="Z32" s="27"/>
+      <c r="AA32" s="27"/>
+      <c r="AB32" s="27"/>
+      <c r="AC32" s="27"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="27" t="s">
+      <c r="A33" s="28" t="s">
         <v>291</v>
       </c>
-      <c r="B33" s="31">
+      <c r="B33" s="32">
         <v>2.13</v>
       </c>
-      <c r="C33" s="31">
+      <c r="C33" s="32">
         <v>2.14</v>
       </c>
-      <c r="D33" s="31">
+      <c r="D33" s="32">
         <v>2.43</v>
       </c>
-      <c r="E33" s="31">
+      <c r="E33" s="32">
         <v>9.72</v>
       </c>
-      <c r="F33" s="31">
+      <c r="F33" s="32">
         <v>2.6</v>
       </c>
-      <c r="G33" s="31">
+      <c r="G33" s="32">
         <v>3.55</v>
       </c>
-      <c r="H33" s="31">
+      <c r="H33" s="32">
         <v>3.43</v>
       </c>
-      <c r="I33" s="31">
+      <c r="I33" s="32">
         <v>2.96</v>
       </c>
-      <c r="J33" s="31">
+      <c r="J33" s="32">
         <v>3.27</v>
       </c>
-      <c r="K33" s="31">
+      <c r="K33" s="32">
         <v>3.15</v>
       </c>
-      <c r="L33" s="31">
+      <c r="L33" s="32">
         <v>2.76</v>
       </c>
-      <c r="M33" s="31">
+      <c r="M33" s="32">
         <v>3.86</v>
       </c>
-      <c r="N33" s="31"/>
-      <c r="O33" s="31">
+      <c r="N33" s="32"/>
+      <c r="O33" s="32">
         <v>6.13</v>
       </c>
-      <c r="P33" s="31">
+      <c r="P33" s="32">
         <v>14.82</v>
       </c>
-      <c r="Q33" s="31">
-        <v>0.0</v>
-      </c>
-      <c r="R33" s="31">
+      <c r="Q33" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="R33" s="32">
         <v>6.44</v>
       </c>
-      <c r="S33" s="31">
+      <c r="S33" s="32">
         <v>4.65</v>
       </c>
-      <c r="T33" s="31">
+      <c r="T33" s="32">
         <v>2.62</v>
       </c>
-      <c r="U33" s="31">
+      <c r="U33" s="32">
         <v>4.29</v>
       </c>
-      <c r="V33" s="31">
+      <c r="V33" s="32">
         <v>4.53</v>
       </c>
-      <c r="W33" s="31">
+      <c r="W33" s="32">
         <v>4.93</v>
       </c>
-      <c r="X33" s="31">
+      <c r="X33" s="32">
         <v>2.36</v>
       </c>
-      <c r="Y33" s="31">
+      <c r="Y33" s="32">
         <v>47.84</v>
       </c>
-      <c r="Z33" s="31">
+      <c r="Z33" s="32">
         <v>1.73</v>
       </c>
-      <c r="AA33" s="31">
+      <c r="AA33" s="32">
         <v>1.99</v>
       </c>
-      <c r="AB33" s="31">
+      <c r="AB33" s="32">
         <v>2.05</v>
       </c>
-      <c r="AC33" s="31">
+      <c r="AC33" s="32">
         <v>2.17</v>
       </c>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="27" t="s">
+      <c r="A34" s="28" t="s">
         <v>292</v>
       </c>
-      <c r="B34" s="31">
+      <c r="B34" s="32">
         <v>3.86</v>
       </c>
-      <c r="C34" s="31">
+      <c r="C34" s="32">
         <v>4.22</v>
       </c>
-      <c r="D34" s="31">
+      <c r="D34" s="32">
         <v>4.62</v>
       </c>
-      <c r="E34" s="31">
+      <c r="E34" s="32">
         <v>4.82</v>
       </c>
-      <c r="F34" s="31">
+      <c r="F34" s="32">
         <v>3.12</v>
       </c>
-      <c r="G34" s="31">
+      <c r="G34" s="32">
         <v>3.26</v>
       </c>
-      <c r="H34" s="31">
+      <c r="H34" s="32">
         <v>3.11</v>
       </c>
-      <c r="I34" s="31">
+      <c r="I34" s="32">
         <v>3.17</v>
       </c>
-      <c r="J34" s="31"/>
-      <c r="K34" s="31"/>
-      <c r="L34" s="31"/>
-      <c r="M34" s="31"/>
-      <c r="N34" s="31"/>
-      <c r="O34" s="31">
+      <c r="J34" s="32"/>
+      <c r="K34" s="32"/>
+      <c r="L34" s="32"/>
+      <c r="M34" s="32"/>
+      <c r="N34" s="32"/>
+      <c r="O34" s="32">
         <v>7.14</v>
       </c>
-      <c r="P34" s="31">
+      <c r="P34" s="32">
         <v>6.2</v>
       </c>
-      <c r="Q34" s="31">
+      <c r="Q34" s="32">
         <v>3.82</v>
       </c>
-      <c r="R34" s="31">
+      <c r="R34" s="32">
         <v>4.34</v>
       </c>
-      <c r="S34" s="31">
+      <c r="S34" s="32">
         <v>4.07</v>
       </c>
-      <c r="T34" s="31">
+      <c r="T34" s="32">
         <v>3.78</v>
       </c>
-      <c r="U34" s="31">
+      <c r="U34" s="32">
         <v>8.8</v>
       </c>
-      <c r="V34" s="31">
+      <c r="V34" s="32">
         <v>9.63</v>
       </c>
-      <c r="W34" s="31">
+      <c r="W34" s="32">
         <v>10.29</v>
       </c>
-      <c r="X34" s="31">
+      <c r="X34" s="32">
         <v>9.69</v>
       </c>
-      <c r="Y34" s="31">
+      <c r="Y34" s="32">
         <v>9.5</v>
       </c>
-      <c r="Z34" s="31"/>
-      <c r="AA34" s="31"/>
-      <c r="AB34" s="31"/>
-      <c r="AC34" s="31"/>
+      <c r="Z34" s="32"/>
+      <c r="AA34" s="32"/>
+      <c r="AB34" s="32"/>
+      <c r="AC34" s="32"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="27" t="s">
+      <c r="A35" s="28" t="s">
         <v>293</v>
       </c>
-      <c r="B35" s="31">
+      <c r="B35" s="32">
         <v>2.13</v>
       </c>
-      <c r="C35" s="31">
+      <c r="C35" s="32">
         <v>2.14</v>
       </c>
-      <c r="D35" s="31">
+      <c r="D35" s="32">
         <v>2.43</v>
       </c>
-      <c r="E35" s="31">
+      <c r="E35" s="32">
         <v>9.72</v>
       </c>
-      <c r="F35" s="31">
+      <c r="F35" s="32">
         <v>2.6</v>
       </c>
-      <c r="G35" s="31">
+      <c r="G35" s="32">
         <v>3.55</v>
       </c>
-      <c r="H35" s="31">
+      <c r="H35" s="32">
         <v>3.43</v>
       </c>
-      <c r="I35" s="31">
+      <c r="I35" s="32">
         <v>2.96</v>
       </c>
-      <c r="J35" s="31">
+      <c r="J35" s="32">
         <v>3.27</v>
       </c>
-      <c r="K35" s="31">
+      <c r="K35" s="32">
         <v>3.15</v>
       </c>
-      <c r="L35" s="31">
+      <c r="L35" s="32">
         <v>2.76</v>
       </c>
-      <c r="M35" s="31">
+      <c r="M35" s="32">
         <v>3.86</v>
       </c>
-      <c r="N35" s="31">
+      <c r="N35" s="32">
         <v>5.68</v>
       </c>
-      <c r="O35" s="31">
+      <c r="O35" s="32">
         <v>6.17</v>
       </c>
-      <c r="P35" s="31">
+      <c r="P35" s="32">
         <v>20.59</v>
       </c>
-      <c r="Q35" s="31">
-        <v>0.0</v>
-      </c>
-      <c r="R35" s="31">
+      <c r="Q35" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="R35" s="32">
         <v>8.94</v>
       </c>
-      <c r="S35" s="31">
+      <c r="S35" s="32">
         <v>6.46</v>
       </c>
-      <c r="T35" s="31">
+      <c r="T35" s="32">
         <v>3.63</v>
       </c>
-      <c r="U35" s="31">
+      <c r="U35" s="32">
         <v>5.95</v>
       </c>
-      <c r="V35" s="31">
+      <c r="V35" s="32">
         <v>6.29</v>
       </c>
-      <c r="W35" s="31">
+      <c r="W35" s="32">
         <v>6.85</v>
       </c>
-      <c r="X35" s="31">
+      <c r="X35" s="32">
         <v>3.28</v>
       </c>
-      <c r="Y35" s="31">
+      <c r="Y35" s="32">
         <v>66.44</v>
       </c>
-      <c r="Z35" s="31">
+      <c r="Z35" s="32">
         <v>2.4</v>
       </c>
-      <c r="AA35" s="31">
+      <c r="AA35" s="32">
         <v>2.65</v>
       </c>
-      <c r="AB35" s="31">
+      <c r="AB35" s="32">
         <v>2.74</v>
       </c>
-      <c r="AC35" s="31">
+      <c r="AC35" s="32">
         <v>2.9</v>
       </c>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="27" t="s">
+      <c r="A36" s="28" t="s">
         <v>294</v>
       </c>
-      <c r="B36" s="31">
+      <c r="B36" s="32">
         <v>3.86</v>
       </c>
-      <c r="C36" s="31">
+      <c r="C36" s="32">
         <v>4.22</v>
       </c>
-      <c r="D36" s="31">
+      <c r="D36" s="32">
         <v>4.62</v>
       </c>
-      <c r="E36" s="31">
+      <c r="E36" s="32">
         <v>4.82</v>
       </c>
-      <c r="F36" s="31">
+      <c r="F36" s="32">
         <v>3.12</v>
       </c>
-      <c r="G36" s="31">
+      <c r="G36" s="32">
         <v>3.26</v>
       </c>
-      <c r="H36" s="31">
+      <c r="H36" s="32">
         <v>3.11</v>
       </c>
-      <c r="I36" s="31">
+      <c r="I36" s="32">
         <v>3.17</v>
       </c>
-      <c r="J36" s="31">
+      <c r="J36" s="32">
         <v>3.61</v>
       </c>
-      <c r="K36" s="31">
+      <c r="K36" s="32">
         <v>4.08</v>
       </c>
-      <c r="L36" s="31">
+      <c r="L36" s="32">
         <v>7.11</v>
       </c>
-      <c r="M36" s="31">
+      <c r="M36" s="32">
         <v>7.8</v>
       </c>
-      <c r="N36" s="31">
+      <c r="N36" s="32">
         <v>9.11</v>
       </c>
-      <c r="O36" s="31">
+      <c r="O36" s="32">
         <v>9.36</v>
       </c>
-      <c r="P36" s="31">
+      <c r="P36" s="32">
         <v>8.61</v>
       </c>
-      <c r="Q36" s="31">
+      <c r="Q36" s="32">
         <v>5.3</v>
       </c>
-      <c r="R36" s="31">
+      <c r="R36" s="32">
         <v>6.02</v>
       </c>
-      <c r="S36" s="31">
+      <c r="S36" s="32">
         <v>5.65</v>
       </c>
-      <c r="T36" s="31">
+      <c r="T36" s="32">
         <v>5.25</v>
       </c>
-      <c r="U36" s="31">
+      <c r="U36" s="32">
         <v>12.22</v>
       </c>
-      <c r="V36" s="31">
+      <c r="V36" s="32">
         <v>13.37</v>
       </c>
-      <c r="W36" s="31">
+      <c r="W36" s="32">
         <v>14.27</v>
       </c>
-      <c r="X36" s="31">
+      <c r="X36" s="32">
         <v>13.42</v>
       </c>
-      <c r="Y36" s="31">
+      <c r="Y36" s="32">
         <v>13.12</v>
       </c>
-      <c r="Z36" s="31"/>
-      <c r="AA36" s="31"/>
-      <c r="AB36" s="31"/>
-      <c r="AC36" s="31"/>
+      <c r="Z36" s="32"/>
+      <c r="AA36" s="32"/>
+      <c r="AB36" s="32"/>
+      <c r="AC36" s="32"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="25" t="s">
+      <c r="A37" s="26" t="s">
         <v>295</v>
       </c>
-      <c r="B37" s="26"/>
-      <c r="C37" s="26"/>
-      <c r="D37" s="26"/>
-      <c r="E37" s="26"/>
-      <c r="F37" s="26"/>
-      <c r="G37" s="26"/>
-      <c r="H37" s="26"/>
-      <c r="I37" s="26"/>
-      <c r="J37" s="26"/>
-      <c r="K37" s="26"/>
-      <c r="L37" s="26"/>
-      <c r="M37" s="26"/>
-      <c r="N37" s="26"/>
-      <c r="O37" s="26"/>
-      <c r="P37" s="26"/>
-      <c r="Q37" s="26"/>
-      <c r="R37" s="26"/>
-      <c r="S37" s="26"/>
-      <c r="T37" s="26"/>
-      <c r="U37" s="26"/>
-      <c r="V37" s="26"/>
-      <c r="W37" s="26"/>
-      <c r="X37" s="26"/>
-      <c r="Y37" s="26"/>
-      <c r="Z37" s="26"/>
-      <c r="AA37" s="26"/>
-      <c r="AB37" s="26"/>
-      <c r="AC37" s="26"/>
+      <c r="B37" s="27"/>
+      <c r="C37" s="27"/>
+      <c r="D37" s="27"/>
+      <c r="E37" s="27"/>
+      <c r="F37" s="27"/>
+      <c r="G37" s="27"/>
+      <c r="H37" s="27"/>
+      <c r="I37" s="27"/>
+      <c r="J37" s="27"/>
+      <c r="K37" s="27"/>
+      <c r="L37" s="27"/>
+      <c r="M37" s="27"/>
+      <c r="N37" s="27"/>
+      <c r="O37" s="27"/>
+      <c r="P37" s="27"/>
+      <c r="Q37" s="27"/>
+      <c r="R37" s="27"/>
+      <c r="S37" s="27"/>
+      <c r="T37" s="27"/>
+      <c r="U37" s="27"/>
+      <c r="V37" s="27"/>
+      <c r="W37" s="27"/>
+      <c r="X37" s="27"/>
+      <c r="Y37" s="27"/>
+      <c r="Z37" s="27"/>
+      <c r="AA37" s="27"/>
+      <c r="AB37" s="27"/>
+      <c r="AC37" s="27"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="27" t="s">
+      <c r="A38" s="28" t="s">
         <v>296</v>
       </c>
-      <c r="B38" s="29">
+      <c r="B38" s="30">
         <v>1.73</v>
       </c>
-      <c r="C38" s="29">
+      <c r="C38" s="30">
         <v>1.86</v>
       </c>
-      <c r="D38" s="29">
+      <c r="D38" s="30">
         <v>1.7</v>
       </c>
-      <c r="E38" s="29">
+      <c r="E38" s="30">
         <v>2.09</v>
       </c>
-      <c r="F38" s="29">
+      <c r="F38" s="30">
         <v>1.72</v>
       </c>
-      <c r="G38" s="29">
+      <c r="G38" s="30">
         <v>1.43</v>
       </c>
-      <c r="H38" s="29">
+      <c r="H38" s="30">
         <v>1.49</v>
       </c>
-      <c r="I38" s="29">
+      <c r="I38" s="30">
         <v>1.88</v>
       </c>
-      <c r="J38" s="29">
+      <c r="J38" s="30">
         <v>1.95</v>
       </c>
-      <c r="K38" s="29">
+      <c r="K38" s="30">
         <v>2.28</v>
       </c>
-      <c r="L38" s="29">
+      <c r="L38" s="30">
         <v>2.61</v>
       </c>
-      <c r="M38" s="29">
+      <c r="M38" s="30">
         <v>2.15</v>
       </c>
-      <c r="N38" s="29">
+      <c r="N38" s="30">
         <v>2.06</v>
       </c>
-      <c r="O38" s="29">
+      <c r="O38" s="30">
         <v>1.93</v>
       </c>
-      <c r="P38" s="29">
+      <c r="P38" s="30">
         <v>2.0</v>
       </c>
-      <c r="Q38" s="29">
+      <c r="Q38" s="30">
         <v>0.84</v>
       </c>
-      <c r="R38" s="29">
+      <c r="R38" s="30">
         <v>1.38</v>
       </c>
-      <c r="S38" s="29">
+      <c r="S38" s="30">
         <v>1.68</v>
       </c>
-      <c r="T38" s="29">
+      <c r="T38" s="30">
         <v>2.06</v>
       </c>
-      <c r="U38" s="29">
+      <c r="U38" s="30">
         <v>2.53</v>
       </c>
-      <c r="V38" s="29">
+      <c r="V38" s="30">
         <v>2.01</v>
       </c>
-      <c r="W38" s="29">
+      <c r="W38" s="30">
         <v>1.11</v>
       </c>
-      <c r="X38" s="29">
+      <c r="X38" s="30">
         <v>0.92</v>
       </c>
-      <c r="Y38" s="29">
+      <c r="Y38" s="30">
         <v>0.91</v>
       </c>
-      <c r="Z38" s="29">
+      <c r="Z38" s="30">
         <v>1.3</v>
       </c>
-      <c r="AA38" s="29">
+      <c r="AA38" s="30">
         <v>0.82</v>
       </c>
-      <c r="AB38" s="29">
+      <c r="AB38" s="30">
         <v>0.92</v>
       </c>
-      <c r="AC38" s="29">
+      <c r="AC38" s="30">
         <v>0.83</v>
       </c>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="27" t="s">
+      <c r="A39" s="28" t="s">
         <v>297</v>
       </c>
-      <c r="B39" s="29">
+      <c r="B39" s="30">
         <v>1.81</v>
       </c>
-      <c r="C39" s="29">
+      <c r="C39" s="30">
         <v>1.77</v>
       </c>
-      <c r="D39" s="29">
+      <c r="D39" s="30">
         <v>1.69</v>
       </c>
-      <c r="E39" s="29">
+      <c r="E39" s="30">
         <v>1.73</v>
       </c>
-      <c r="F39" s="29">
+      <c r="F39" s="30">
         <v>1.68</v>
       </c>
-      <c r="G39" s="29">
+      <c r="G39" s="30">
         <v>1.76</v>
       </c>
-      <c r="H39" s="29">
+      <c r="H39" s="30">
         <v>1.98</v>
       </c>
-      <c r="I39" s="29">
+      <c r="I39" s="30">
         <v>2.14</v>
       </c>
-      <c r="J39" s="29">
+      <c r="J39" s="30">
         <v>2.2</v>
       </c>
-      <c r="K39" s="29">
+      <c r="K39" s="30">
         <v>2.22</v>
       </c>
-      <c r="L39" s="29">
+      <c r="L39" s="30">
         <v>2.17</v>
       </c>
-      <c r="M39" s="29">
+      <c r="M39" s="30">
         <v>1.77</v>
       </c>
-      <c r="N39" s="29">
+      <c r="N39" s="30">
         <v>1.61</v>
       </c>
-      <c r="O39" s="29">
+      <c r="O39" s="30">
         <v>1.54</v>
       </c>
-      <c r="P39" s="29">
+      <c r="P39" s="30">
         <v>1.57</v>
       </c>
-      <c r="Q39" s="29">
+      <c r="Q39" s="30">
         <v>1.66</v>
       </c>
-      <c r="R39" s="29">
+      <c r="R39" s="30">
         <v>1.92</v>
       </c>
-      <c r="S39" s="29">
+      <c r="S39" s="30">
         <v>1.9</v>
       </c>
-      <c r="T39" s="29">
+      <c r="T39" s="30">
         <v>1.79</v>
       </c>
-      <c r="U39" s="29">
+      <c r="U39" s="30">
         <v>1.57</v>
       </c>
-      <c r="V39" s="29">
+      <c r="V39" s="30">
         <v>1.28</v>
       </c>
-      <c r="W39" s="29">
+      <c r="W39" s="30">
         <v>1.0</v>
       </c>
-      <c r="X39" s="29">
+      <c r="X39" s="30">
         <v>0.96</v>
       </c>
-      <c r="Y39" s="29">
+      <c r="Y39" s="30">
         <v>0.94</v>
       </c>
-      <c r="Z39" s="30"/>
-      <c r="AA39" s="30"/>
-      <c r="AB39" s="30"/>
-      <c r="AC39" s="30"/>
+      <c r="Z39" s="31"/>
+      <c r="AA39" s="31"/>
+      <c r="AB39" s="31"/>
+      <c r="AC39" s="31"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="25" t="s">
+      <c r="A40" s="26" t="s">
         <v>298</v>
       </c>
-      <c r="B40" s="26"/>
-      <c r="C40" s="26"/>
-      <c r="D40" s="26"/>
-      <c r="E40" s="26"/>
-      <c r="F40" s="26"/>
-      <c r="G40" s="26"/>
-      <c r="H40" s="26"/>
-      <c r="I40" s="26"/>
-      <c r="J40" s="26"/>
-      <c r="K40" s="26"/>
-      <c r="L40" s="26"/>
-      <c r="M40" s="26"/>
-      <c r="N40" s="26"/>
-      <c r="O40" s="26"/>
-      <c r="P40" s="26"/>
-      <c r="Q40" s="26"/>
-      <c r="R40" s="26"/>
-      <c r="S40" s="26"/>
-      <c r="T40" s="26"/>
-      <c r="U40" s="26"/>
-      <c r="V40" s="26"/>
-      <c r="W40" s="26"/>
-      <c r="X40" s="26"/>
-      <c r="Y40" s="26"/>
-      <c r="Z40" s="26"/>
-      <c r="AA40" s="26"/>
-      <c r="AB40" s="26"/>
-      <c r="AC40" s="26"/>
+      <c r="B40" s="27"/>
+      <c r="C40" s="27"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="27"/>
+      <c r="G40" s="27"/>
+      <c r="H40" s="27"/>
+      <c r="I40" s="27"/>
+      <c r="J40" s="27"/>
+      <c r="K40" s="27"/>
+      <c r="L40" s="27"/>
+      <c r="M40" s="27"/>
+      <c r="N40" s="27"/>
+      <c r="O40" s="27"/>
+      <c r="P40" s="27"/>
+      <c r="Q40" s="27"/>
+      <c r="R40" s="27"/>
+      <c r="S40" s="27"/>
+      <c r="T40" s="27"/>
+      <c r="U40" s="27"/>
+      <c r="V40" s="27"/>
+      <c r="W40" s="27"/>
+      <c r="X40" s="27"/>
+      <c r="Y40" s="27"/>
+      <c r="Z40" s="27"/>
+      <c r="AA40" s="27"/>
+      <c r="AB40" s="27"/>
+      <c r="AC40" s="27"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="27" t="s">
+      <c r="A41" s="28" t="s">
         <v>299</v>
       </c>
-      <c r="B41" s="29">
+      <c r="B41" s="30">
         <v>2.44</v>
       </c>
-      <c r="C41" s="29">
+      <c r="C41" s="30">
         <v>2.77</v>
       </c>
-      <c r="D41" s="29">
+      <c r="D41" s="30">
         <v>1.87</v>
       </c>
-      <c r="E41" s="29">
+      <c r="E41" s="30">
         <v>2.32</v>
       </c>
-      <c r="F41" s="29">
+      <c r="F41" s="30">
         <v>1.89</v>
       </c>
-      <c r="G41" s="29">
+      <c r="G41" s="30">
         <v>1.62</v>
       </c>
-      <c r="H41" s="29">
+      <c r="H41" s="30">
         <v>1.67</v>
       </c>
-      <c r="I41" s="29">
+      <c r="I41" s="30">
         <v>1.9</v>
       </c>
-      <c r="J41" s="29">
+      <c r="J41" s="30">
         <v>2.0</v>
       </c>
-      <c r="K41" s="29">
+      <c r="K41" s="30">
         <v>2.33</v>
       </c>
-      <c r="L41" s="29">
+      <c r="L41" s="30">
         <v>2.71</v>
       </c>
-      <c r="M41" s="29">
+      <c r="M41" s="30">
         <v>2.23</v>
       </c>
-      <c r="N41" s="29">
+      <c r="N41" s="30">
         <v>2.12</v>
       </c>
-      <c r="O41" s="29">
+      <c r="O41" s="30">
         <v>2.01</v>
       </c>
-      <c r="P41" s="29">
+      <c r="P41" s="30">
         <v>2.12</v>
       </c>
-      <c r="Q41" s="29">
+      <c r="Q41" s="30">
         <v>0.89</v>
       </c>
-      <c r="R41" s="29">
+      <c r="R41" s="30">
         <v>1.5</v>
       </c>
-      <c r="S41" s="29">
+      <c r="S41" s="30">
         <v>1.15</v>
       </c>
-      <c r="T41" s="29">
+      <c r="T41" s="30">
         <v>1.4</v>
       </c>
-      <c r="U41" s="29">
+      <c r="U41" s="30">
         <v>1.75</v>
       </c>
-      <c r="V41" s="29">
+      <c r="V41" s="30">
         <v>1.41</v>
       </c>
-      <c r="W41" s="29">
+      <c r="W41" s="30">
         <v>0.74</v>
       </c>
-      <c r="X41" s="29">
+      <c r="X41" s="30">
         <v>0.61</v>
       </c>
-      <c r="Y41" s="29">
+      <c r="Y41" s="30">
         <v>0.6</v>
       </c>
-      <c r="Z41" s="29">
+      <c r="Z41" s="30">
         <v>1.33</v>
       </c>
-      <c r="AA41" s="29">
+      <c r="AA41" s="30">
         <v>0.82</v>
       </c>
-      <c r="AB41" s="29">
+      <c r="AB41" s="30">
         <v>0.92</v>
       </c>
-      <c r="AC41" s="29">
+      <c r="AC41" s="30">
         <v>0.83</v>
       </c>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="27" t="s">
+      <c r="A42" s="28" t="s">
         <v>300</v>
       </c>
-      <c r="B42" s="29">
+      <c r="B42" s="30">
         <v>2.23</v>
       </c>
-      <c r="C42" s="29">
+      <c r="C42" s="30">
         <v>2.08</v>
       </c>
-      <c r="D42" s="29">
+      <c r="D42" s="30">
         <v>1.89</v>
       </c>
-      <c r="E42" s="29">
+      <c r="E42" s="30">
         <v>1.89</v>
       </c>
-      <c r="F42" s="29">
+      <c r="F42" s="30">
         <v>1.82</v>
       </c>
-      <c r="G42" s="29">
+      <c r="G42" s="30">
         <v>1.88</v>
       </c>
-      <c r="H42" s="29">
+      <c r="H42" s="30">
         <v>2.07</v>
       </c>
-      <c r="I42" s="29">
+      <c r="I42" s="30">
         <v>2.2</v>
       </c>
-      <c r="J42" s="29">
+      <c r="J42" s="30">
         <v>2.27</v>
       </c>
-      <c r="K42" s="29">
+      <c r="K42" s="30">
         <v>2.3</v>
       </c>
-      <c r="L42" s="29">
+      <c r="L42" s="30">
         <v>2.25</v>
       </c>
-      <c r="M42" s="29">
+      <c r="M42" s="30">
         <v>1.85</v>
       </c>
-      <c r="N42" s="29">
+      <c r="N42" s="30">
         <v>1.7</v>
       </c>
-      <c r="O42" s="29">
+      <c r="O42" s="30">
         <v>1.46</v>
       </c>
-      <c r="P42" s="29">
+      <c r="P42" s="30">
         <v>1.36</v>
       </c>
-      <c r="Q42" s="29">
+      <c r="Q42" s="30">
         <v>1.34</v>
       </c>
-      <c r="R42" s="29">
+      <c r="R42" s="30">
         <v>1.42</v>
       </c>
-      <c r="S42" s="29">
+      <c r="S42" s="30">
         <v>1.3</v>
       </c>
-      <c r="T42" s="29">
+      <c r="T42" s="30">
         <v>1.22</v>
       </c>
-      <c r="U42" s="29">
+      <c r="U42" s="30">
         <v>1.06</v>
       </c>
-      <c r="V42" s="29">
+      <c r="V42" s="30">
         <v>0.92</v>
       </c>
-      <c r="W42" s="29">
+      <c r="W42" s="30">
         <v>0.78</v>
       </c>
-      <c r="X42" s="29">
+      <c r="X42" s="30">
         <v>0.81</v>
       </c>
-      <c r="Y42" s="29">
+      <c r="Y42" s="30">
         <v>0.87</v>
       </c>
-      <c r="Z42" s="30"/>
-      <c r="AA42" s="30"/>
-      <c r="AB42" s="30"/>
-      <c r="AC42" s="30"/>
+      <c r="Z42" s="31"/>
+      <c r="AA42" s="31"/>
+      <c r="AB42" s="31"/>
+      <c r="AC42" s="31"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="25" t="s">
+      <c r="A43" s="26" t="s">
         <v>301</v>
       </c>
-      <c r="B43" s="26"/>
-      <c r="C43" s="26"/>
-      <c r="D43" s="26"/>
-      <c r="E43" s="26"/>
-      <c r="F43" s="26"/>
-      <c r="G43" s="26"/>
-      <c r="H43" s="26"/>
-      <c r="I43" s="26"/>
-      <c r="J43" s="26"/>
-      <c r="K43" s="26"/>
-      <c r="L43" s="26"/>
-      <c r="M43" s="26"/>
-      <c r="N43" s="26"/>
-      <c r="O43" s="26"/>
-      <c r="P43" s="26"/>
-      <c r="Q43" s="26"/>
-      <c r="R43" s="26"/>
-      <c r="S43" s="26"/>
-      <c r="T43" s="26"/>
-      <c r="U43" s="26"/>
-      <c r="V43" s="26"/>
-      <c r="W43" s="26"/>
-      <c r="X43" s="26"/>
-      <c r="Y43" s="26"/>
-      <c r="Z43" s="26"/>
-      <c r="AA43" s="26"/>
-      <c r="AB43" s="26"/>
-      <c r="AC43" s="26"/>
+      <c r="B43" s="27"/>
+      <c r="C43" s="27"/>
+      <c r="D43" s="27"/>
+      <c r="E43" s="27"/>
+      <c r="F43" s="27"/>
+      <c r="G43" s="27"/>
+      <c r="H43" s="27"/>
+      <c r="I43" s="27"/>
+      <c r="J43" s="27"/>
+      <c r="K43" s="27"/>
+      <c r="L43" s="27"/>
+      <c r="M43" s="27"/>
+      <c r="N43" s="27"/>
+      <c r="O43" s="27"/>
+      <c r="P43" s="27"/>
+      <c r="Q43" s="27"/>
+      <c r="R43" s="27"/>
+      <c r="S43" s="27"/>
+      <c r="T43" s="27"/>
+      <c r="U43" s="27"/>
+      <c r="V43" s="27"/>
+      <c r="W43" s="27"/>
+      <c r="X43" s="27"/>
+      <c r="Y43" s="27"/>
+      <c r="Z43" s="27"/>
+      <c r="AA43" s="27"/>
+      <c r="AB43" s="27"/>
+      <c r="AC43" s="27"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="27" t="s">
+      <c r="A44" s="28" t="s">
         <v>302</v>
       </c>
-      <c r="B44" s="29">
+      <c r="B44" s="30">
         <v>0.57</v>
       </c>
-      <c r="C44" s="29">
+      <c r="C44" s="30">
         <v>0.64</v>
       </c>
-      <c r="D44" s="29">
+      <c r="D44" s="30">
         <v>0.73</v>
       </c>
-      <c r="E44" s="29">
+      <c r="E44" s="30">
         <v>0.86</v>
       </c>
-      <c r="F44" s="29">
+      <c r="F44" s="30">
         <v>0.86</v>
       </c>
-      <c r="G44" s="29">
+      <c r="G44" s="30">
         <v>0.68</v>
       </c>
-      <c r="H44" s="29">
+      <c r="H44" s="30">
         <v>0.63</v>
       </c>
-      <c r="I44" s="29">
+      <c r="I44" s="30">
         <v>0.74</v>
       </c>
-      <c r="J44" s="29">
+      <c r="J44" s="30">
         <v>0.72</v>
       </c>
-      <c r="K44" s="29">
+      <c r="K44" s="30">
         <v>0.78</v>
       </c>
-      <c r="L44" s="29">
+      <c r="L44" s="30">
         <v>0.87</v>
       </c>
-      <c r="M44" s="29">
+      <c r="M44" s="30">
         <v>0.69</v>
       </c>
-      <c r="N44" s="29">
+      <c r="N44" s="30">
         <v>0.63</v>
       </c>
-      <c r="O44" s="29">
+      <c r="O44" s="30">
         <v>0.39</v>
       </c>
-      <c r="P44" s="29">
+      <c r="P44" s="30">
         <v>0.63</v>
       </c>
-      <c r="Q44" s="29">
+      <c r="Q44" s="30">
         <v>0.38</v>
       </c>
-      <c r="R44" s="29">
+      <c r="R44" s="30">
         <v>0.5</v>
       </c>
-      <c r="S44" s="29">
+      <c r="S44" s="30">
         <v>0.55</v>
       </c>
-      <c r="T44" s="29">
+      <c r="T44" s="30">
         <v>0.65</v>
       </c>
-      <c r="U44" s="29">
+      <c r="U44" s="30">
         <v>0.77</v>
       </c>
-      <c r="V44" s="29">
+      <c r="V44" s="30">
         <v>0.72</v>
       </c>
-      <c r="W44" s="29">
+      <c r="W44" s="30">
         <v>0.37</v>
       </c>
-      <c r="X44" s="29">
+      <c r="X44" s="30">
         <v>0.33</v>
       </c>
-      <c r="Y44" s="29">
+      <c r="Y44" s="30">
         <v>0.17</v>
       </c>
-      <c r="Z44" s="29">
+      <c r="Z44" s="30">
         <v>0.19</v>
       </c>
-      <c r="AA44" s="29">
+      <c r="AA44" s="30">
         <v>0.26</v>
       </c>
-      <c r="AB44" s="29">
+      <c r="AB44" s="30">
         <v>0.28</v>
       </c>
-      <c r="AC44" s="29">
+      <c r="AC44" s="30">
         <v>0.31</v>
       </c>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="27" t="s">
+      <c r="A45" s="28" t="s">
         <v>303</v>
       </c>
-      <c r="B45" s="29">
+      <c r="B45" s="30">
         <v>0.71</v>
       </c>
-      <c r="C45" s="29">
+      <c r="C45" s="30">
         <v>0.75</v>
       </c>
-      <c r="D45" s="29">
+      <c r="D45" s="30">
         <v>0.76</v>
       </c>
-      <c r="E45" s="29">
+      <c r="E45" s="30">
         <v>0.76</v>
       </c>
-      <c r="F45" s="29">
+      <c r="F45" s="30">
         <v>0.73</v>
       </c>
-      <c r="G45" s="29">
+      <c r="G45" s="30">
         <v>0.71</v>
       </c>
-      <c r="H45" s="29">
+      <c r="H45" s="30">
         <v>0.74</v>
       </c>
-      <c r="I45" s="29">
+      <c r="I45" s="30">
         <v>0.76</v>
       </c>
-      <c r="J45" s="29">
+      <c r="J45" s="30">
         <v>0.74</v>
       </c>
-      <c r="K45" s="29">
+      <c r="K45" s="30">
         <v>0.65</v>
       </c>
-      <c r="L45" s="29">
+      <c r="L45" s="30">
         <v>0.62</v>
       </c>
-      <c r="M45" s="29">
+      <c r="M45" s="30">
         <v>0.54</v>
       </c>
-      <c r="N45" s="29">
+      <c r="N45" s="30">
         <v>0.5</v>
       </c>
-      <c r="O45" s="29">
+      <c r="O45" s="30">
         <v>0.48</v>
       </c>
-      <c r="P45" s="29">
+      <c r="P45" s="30">
         <v>0.55</v>
       </c>
-      <c r="Q45" s="29">
+      <c r="Q45" s="30">
         <v>0.58</v>
       </c>
-      <c r="R45" s="29">
+      <c r="R45" s="30">
         <v>0.64</v>
       </c>
-      <c r="S45" s="29">
+      <c r="S45" s="30">
         <v>0.62</v>
       </c>
-      <c r="T45" s="29">
+      <c r="T45" s="30">
         <v>0.59</v>
       </c>
-      <c r="U45" s="29">
+      <c r="U45" s="30">
         <v>0.45</v>
       </c>
-      <c r="V45" s="29">
+      <c r="V45" s="30">
         <v>0.31</v>
       </c>
-      <c r="W45" s="29">
+      <c r="W45" s="30">
         <v>0.24</v>
       </c>
-      <c r="X45" s="29">
+      <c r="X45" s="30">
         <v>0.23</v>
       </c>
-      <c r="Y45" s="29">
+      <c r="Y45" s="30">
         <v>0.23</v>
       </c>
-      <c r="Z45" s="30"/>
-      <c r="AA45" s="30"/>
-      <c r="AB45" s="30"/>
-      <c r="AC45" s="30"/>
+      <c r="Z45" s="31"/>
+      <c r="AA45" s="31"/>
+      <c r="AB45" s="31"/>
+      <c r="AC45" s="31"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="25" t="s">
+      <c r="A46" s="26" t="s">
         <v>304</v>
       </c>
-      <c r="B46" s="26"/>
-      <c r="C46" s="26"/>
-      <c r="D46" s="26"/>
-      <c r="E46" s="26"/>
-      <c r="F46" s="26"/>
-      <c r="G46" s="26"/>
-      <c r="H46" s="26"/>
-      <c r="I46" s="26"/>
-      <c r="J46" s="26"/>
-      <c r="K46" s="26"/>
-      <c r="L46" s="26"/>
-      <c r="M46" s="26"/>
-      <c r="N46" s="26"/>
-      <c r="O46" s="26"/>
-      <c r="P46" s="26"/>
-      <c r="Q46" s="26"/>
-      <c r="R46" s="26"/>
-      <c r="S46" s="26"/>
-      <c r="T46" s="26"/>
-      <c r="U46" s="26"/>
-      <c r="V46" s="26"/>
-      <c r="W46" s="26"/>
-      <c r="X46" s="26"/>
-      <c r="Y46" s="26"/>
-      <c r="Z46" s="26"/>
-      <c r="AA46" s="26"/>
-      <c r="AB46" s="26"/>
-      <c r="AC46" s="26"/>
+      <c r="B46" s="27"/>
+      <c r="C46" s="27"/>
+      <c r="D46" s="27"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="27"/>
+      <c r="G46" s="27"/>
+      <c r="H46" s="27"/>
+      <c r="I46" s="27"/>
+      <c r="J46" s="27"/>
+      <c r="K46" s="27"/>
+      <c r="L46" s="27"/>
+      <c r="M46" s="27"/>
+      <c r="N46" s="27"/>
+      <c r="O46" s="27"/>
+      <c r="P46" s="27"/>
+      <c r="Q46" s="27"/>
+      <c r="R46" s="27"/>
+      <c r="S46" s="27"/>
+      <c r="T46" s="27"/>
+      <c r="U46" s="27"/>
+      <c r="V46" s="27"/>
+      <c r="W46" s="27"/>
+      <c r="X46" s="27"/>
+      <c r="Y46" s="27"/>
+      <c r="Z46" s="27"/>
+      <c r="AA46" s="27"/>
+      <c r="AB46" s="27"/>
+      <c r="AC46" s="27"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="27" t="s">
+      <c r="A47" s="28" t="s">
         <v>305</v>
       </c>
-      <c r="B47" s="29">
+      <c r="B47" s="30">
         <v>8.98</v>
       </c>
-      <c r="C47" s="29">
+      <c r="C47" s="30">
         <v>8.8</v>
       </c>
-      <c r="D47" s="29">
+      <c r="D47" s="30">
         <v>15.22</v>
       </c>
-      <c r="E47" s="30"/>
-      <c r="F47" s="29">
+      <c r="E47" s="31"/>
+      <c r="F47" s="30">
         <v>7.39</v>
       </c>
-      <c r="G47" s="29">
+      <c r="G47" s="30">
         <v>6.36</v>
       </c>
-      <c r="H47" s="30"/>
-      <c r="I47" s="29">
+      <c r="H47" s="31"/>
+      <c r="I47" s="30">
         <v>17.24</v>
       </c>
-      <c r="J47" s="29">
+      <c r="J47" s="30">
         <v>11.04</v>
       </c>
-      <c r="K47" s="29">
+      <c r="K47" s="30">
         <v>33.32</v>
       </c>
-      <c r="L47" s="30"/>
-      <c r="M47" s="29">
+      <c r="L47" s="31"/>
+      <c r="M47" s="30">
         <v>11.62</v>
       </c>
-      <c r="N47" s="29">
+      <c r="N47" s="30">
         <v>7.97</v>
       </c>
-      <c r="O47" s="29">
+      <c r="O47" s="30">
         <v>14.33</v>
       </c>
-      <c r="P47" s="30"/>
-      <c r="Q47" s="29">
+      <c r="P47" s="31"/>
+      <c r="Q47" s="30">
         <v>3.94</v>
       </c>
-      <c r="R47" s="29">
+      <c r="R47" s="30">
         <v>5.94</v>
       </c>
-      <c r="S47" s="29">
+      <c r="S47" s="30">
         <v>9.85</v>
       </c>
-      <c r="T47" s="29">
+      <c r="T47" s="30">
         <v>59.52</v>
       </c>
-      <c r="U47" s="30"/>
-      <c r="V47" s="30"/>
-      <c r="W47" s="29">
+      <c r="U47" s="31"/>
+      <c r="V47" s="31"/>
+      <c r="W47" s="30">
         <v>4.4</v>
       </c>
-      <c r="X47" s="29">
+      <c r="X47" s="30">
         <v>10.07</v>
       </c>
-      <c r="Y47" s="29">
+      <c r="Y47" s="30">
         <v>3.86</v>
       </c>
-      <c r="Z47" s="28">
+      <c r="Z47" s="29">
         <v>124.64</v>
       </c>
-      <c r="AA47" s="29">
+      <c r="AA47" s="30">
         <v>2.67</v>
       </c>
-      <c r="AB47" s="30"/>
-      <c r="AC47" s="29">
+      <c r="AB47" s="31"/>
+      <c r="AC47" s="30">
         <v>3.0</v>
       </c>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="27" t="s">
+      <c r="A48" s="28" t="s">
         <v>306</v>
       </c>
-      <c r="B48" s="29">
+      <c r="B48" s="30">
         <v>12.13</v>
       </c>
-      <c r="C48" s="29">
+      <c r="C48" s="30">
         <v>11.61</v>
       </c>
-      <c r="D48" s="29">
+      <c r="D48" s="30">
         <v>16.92</v>
       </c>
-      <c r="E48" s="29">
+      <c r="E48" s="30">
         <v>17.44</v>
       </c>
-      <c r="F48" s="29">
+      <c r="F48" s="30">
         <v>12.11</v>
       </c>
-      <c r="G48" s="29">
+      <c r="G48" s="30">
         <v>17.11</v>
       </c>
-      <c r="H48" s="29">
+      <c r="H48" s="30">
         <v>65.76</v>
       </c>
-      <c r="I48" s="29">
+      <c r="I48" s="30">
         <v>26.97</v>
       </c>
-      <c r="J48" s="29">
+      <c r="J48" s="30">
         <v>21.88</v>
       </c>
-      <c r="K48" s="29">
+      <c r="K48" s="30">
         <v>25.72</v>
       </c>
-      <c r="L48" s="29">
+      <c r="L48" s="30">
         <v>31.31</v>
       </c>
-      <c r="M48" s="29">
+      <c r="M48" s="30">
         <v>11.35</v>
       </c>
-      <c r="N48" s="29">
+      <c r="N48" s="30">
         <v>9.8</v>
       </c>
-      <c r="O48" s="29">
+      <c r="O48" s="30">
         <v>10.42</v>
       </c>
-      <c r="P48" s="29">
+      <c r="P48" s="30">
         <v>12.27</v>
       </c>
-      <c r="Q48" s="29">
+      <c r="Q48" s="30">
         <v>12.71</v>
       </c>
-      <c r="R48" s="29">
+      <c r="R48" s="30">
         <v>24.19</v>
       </c>
-      <c r="S48" s="29">
+      <c r="S48" s="30">
         <v>25.8</v>
       </c>
-      <c r="T48" s="29">
+      <c r="T48" s="30">
         <v>34.86</v>
       </c>
-      <c r="U48" s="29">
+      <c r="U48" s="30">
         <v>17.55</v>
       </c>
-      <c r="V48" s="29">
+      <c r="V48" s="30">
         <v>12.66</v>
       </c>
-      <c r="W48" s="29">
+      <c r="W48" s="30">
         <v>5.26</v>
       </c>
-      <c r="X48" s="29">
+      <c r="X48" s="30">
         <v>17.8</v>
       </c>
-      <c r="Y48" s="29">
+      <c r="Y48" s="30">
         <v>9.81</v>
       </c>
-      <c r="Z48" s="30"/>
-      <c r="AA48" s="30"/>
-      <c r="AB48" s="30"/>
-      <c r="AC48" s="30"/>
+      <c r="Z48" s="31"/>
+      <c r="AA48" s="31"/>
+      <c r="AB48" s="31"/>
+      <c r="AC48" s="31"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="25" t="s">
+      <c r="A49" s="26" t="s">
         <v>307</v>
       </c>
-      <c r="B49" s="26"/>
-      <c r="C49" s="26"/>
-      <c r="D49" s="26"/>
-      <c r="E49" s="26"/>
-      <c r="F49" s="26"/>
-      <c r="G49" s="26"/>
-      <c r="H49" s="26"/>
-      <c r="I49" s="26"/>
-      <c r="J49" s="26"/>
-      <c r="K49" s="26"/>
-      <c r="L49" s="26"/>
-      <c r="M49" s="26"/>
-      <c r="N49" s="26"/>
-      <c r="O49" s="26"/>
-      <c r="P49" s="26"/>
-      <c r="Q49" s="26"/>
-      <c r="R49" s="26"/>
-      <c r="S49" s="26"/>
-      <c r="T49" s="26"/>
-      <c r="U49" s="26"/>
-      <c r="V49" s="26"/>
-      <c r="W49" s="26"/>
-      <c r="X49" s="26"/>
-      <c r="Y49" s="26"/>
-      <c r="Z49" s="26"/>
-      <c r="AA49" s="26"/>
-      <c r="AB49" s="26"/>
-      <c r="AC49" s="26"/>
+      <c r="B49" s="27"/>
+      <c r="C49" s="27"/>
+      <c r="D49" s="27"/>
+      <c r="E49" s="27"/>
+      <c r="F49" s="27"/>
+      <c r="G49" s="27"/>
+      <c r="H49" s="27"/>
+      <c r="I49" s="27"/>
+      <c r="J49" s="27"/>
+      <c r="K49" s="27"/>
+      <c r="L49" s="27"/>
+      <c r="M49" s="27"/>
+      <c r="N49" s="27"/>
+      <c r="O49" s="27"/>
+      <c r="P49" s="27"/>
+      <c r="Q49" s="27"/>
+      <c r="R49" s="27"/>
+      <c r="S49" s="27"/>
+      <c r="T49" s="27"/>
+      <c r="U49" s="27"/>
+      <c r="V49" s="27"/>
+      <c r="W49" s="27"/>
+      <c r="X49" s="27"/>
+      <c r="Y49" s="27"/>
+      <c r="Z49" s="27"/>
+      <c r="AA49" s="27"/>
+      <c r="AB49" s="27"/>
+      <c r="AC49" s="27"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="27" t="s">
+      <c r="A50" s="28" t="s">
         <v>308</v>
       </c>
-      <c r="B50" s="29">
+      <c r="B50" s="30">
         <v>7.39</v>
       </c>
-      <c r="C50" s="29">
+      <c r="C50" s="30">
         <v>8.04</v>
       </c>
-      <c r="D50" s="29">
+      <c r="D50" s="30">
         <v>7.92</v>
       </c>
-      <c r="E50" s="29">
+      <c r="E50" s="30">
         <v>9.15</v>
       </c>
-      <c r="F50" s="29">
+      <c r="F50" s="30">
         <v>8.23</v>
       </c>
-      <c r="G50" s="29">
+      <c r="G50" s="30">
         <v>12.04</v>
       </c>
-      <c r="H50" s="29">
+      <c r="H50" s="30">
         <v>8.81</v>
       </c>
-      <c r="I50" s="29">
+      <c r="I50" s="30">
         <v>9.03</v>
       </c>
-      <c r="J50" s="29">
+      <c r="J50" s="30">
         <v>10.04</v>
       </c>
-      <c r="K50" s="29">
+      <c r="K50" s="30">
         <v>9.93</v>
       </c>
-      <c r="L50" s="29">
+      <c r="L50" s="30">
         <v>15.27</v>
       </c>
-      <c r="M50" s="29">
+      <c r="M50" s="30">
         <v>10.87</v>
       </c>
-      <c r="N50" s="29">
+      <c r="N50" s="30">
         <v>11.46</v>
       </c>
-      <c r="O50" s="29">
+      <c r="O50" s="30">
         <v>6.12</v>
       </c>
-      <c r="P50" s="29">
+      <c r="P50" s="30">
         <v>8.09</v>
       </c>
-      <c r="Q50" s="29">
+      <c r="Q50" s="30">
         <v>0.03</v>
       </c>
-      <c r="R50" s="29">
+      <c r="R50" s="30">
         <v>0.02</v>
       </c>
-      <c r="S50" s="29">
+      <c r="S50" s="30">
         <v>8.72</v>
       </c>
-      <c r="T50" s="29">
+      <c r="T50" s="30">
         <v>10.75</v>
       </c>
-      <c r="U50" s="29">
+      <c r="U50" s="30">
         <v>14.06</v>
       </c>
-      <c r="V50" s="29">
+      <c r="V50" s="30">
         <v>8.85</v>
       </c>
-      <c r="W50" s="29">
+      <c r="W50" s="30">
         <v>5.36</v>
       </c>
-      <c r="X50" s="29">
+      <c r="X50" s="30">
         <v>5.04</v>
       </c>
-      <c r="Y50" s="29">
+      <c r="Y50" s="30">
         <v>2.81</v>
       </c>
-      <c r="Z50" s="29">
+      <c r="Z50" s="30">
         <v>3.49</v>
       </c>
-      <c r="AA50" s="29">
+      <c r="AA50" s="30">
         <v>4.67</v>
       </c>
-      <c r="AB50" s="29">
+      <c r="AB50" s="30">
         <v>4.65</v>
       </c>
-      <c r="AC50" s="29">
+      <c r="AC50" s="30">
         <v>4.99</v>
       </c>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="27" t="s">
+      <c r="A51" s="28" t="s">
         <v>309</v>
       </c>
-      <c r="B51" s="29">
+      <c r="B51" s="30">
         <v>8.1</v>
       </c>
-      <c r="C51" s="29">
+      <c r="C51" s="30">
         <v>8.7</v>
       </c>
-      <c r="D51" s="29">
+      <c r="D51" s="30">
         <v>8.91</v>
       </c>
-      <c r="E51" s="29">
+      <c r="E51" s="30">
         <v>9.2</v>
       </c>
-      <c r="F51" s="29">
+      <c r="F51" s="30">
         <v>9.36</v>
       </c>
-      <c r="G51" s="29">
+      <c r="G51" s="30">
         <v>9.81</v>
       </c>
-      <c r="H51" s="29">
+      <c r="H51" s="30">
         <v>10.22</v>
       </c>
-      <c r="I51" s="29">
+      <c r="I51" s="30">
         <v>10.65</v>
       </c>
-      <c r="J51" s="29">
+      <c r="J51" s="30">
         <v>11.25</v>
       </c>
-      <c r="K51" s="29">
+      <c r="K51" s="30">
         <v>10.22</v>
       </c>
-      <c r="L51" s="29">
+      <c r="L51" s="30">
         <v>9.86</v>
       </c>
-      <c r="M51" s="29">
+      <c r="M51" s="30">
         <v>0.26</v>
       </c>
-      <c r="N51" s="29">
+      <c r="N51" s="30">
         <v>0.09</v>
       </c>
-      <c r="O51" s="29">
+      <c r="O51" s="30">
         <v>0.09</v>
       </c>
-      <c r="P51" s="29">
+      <c r="P51" s="30">
         <v>0.09</v>
       </c>
-      <c r="Q51" s="29">
+      <c r="Q51" s="30">
         <v>0.09</v>
       </c>
-      <c r="R51" s="29">
+      <c r="R51" s="30">
         <v>0.16</v>
       </c>
-      <c r="S51" s="29">
+      <c r="S51" s="30">
         <v>9.59</v>
       </c>
-      <c r="T51" s="29">
+      <c r="T51" s="30">
         <v>9.09</v>
       </c>
-      <c r="U51" s="29">
+      <c r="U51" s="30">
         <v>7.06</v>
       </c>
-      <c r="V51" s="29">
+      <c r="V51" s="30">
         <v>4.92</v>
       </c>
-      <c r="W51" s="29">
+      <c r="W51" s="30">
         <v>4.06</v>
       </c>
-      <c r="X51" s="29">
+      <c r="X51" s="30">
         <v>3.96</v>
       </c>
-      <c r="Y51" s="29">
+      <c r="Y51" s="30">
         <v>3.97</v>
       </c>
-      <c r="Z51" s="30"/>
-      <c r="AA51" s="30"/>
-      <c r="AB51" s="30"/>
-      <c r="AC51" s="30"/>
+      <c r="Z51" s="31"/>
+      <c r="AA51" s="31"/>
+      <c r="AB51" s="31"/>
+      <c r="AC51" s="31"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="25" t="s">
+      <c r="A52" s="26" t="s">
         <v>310</v>
       </c>
-      <c r="B52" s="26"/>
-      <c r="C52" s="26"/>
-      <c r="D52" s="26"/>
-      <c r="E52" s="26"/>
-      <c r="F52" s="26"/>
-      <c r="G52" s="26"/>
-      <c r="H52" s="26"/>
-      <c r="I52" s="26"/>
-      <c r="J52" s="26"/>
-      <c r="K52" s="26"/>
-      <c r="L52" s="26"/>
-      <c r="M52" s="26"/>
-      <c r="N52" s="26"/>
-      <c r="O52" s="26"/>
-      <c r="P52" s="26"/>
-      <c r="Q52" s="26"/>
-      <c r="R52" s="26"/>
-      <c r="S52" s="26"/>
-      <c r="T52" s="26"/>
-      <c r="U52" s="26"/>
-      <c r="V52" s="26"/>
-      <c r="W52" s="26"/>
-      <c r="X52" s="26"/>
-      <c r="Y52" s="26"/>
-      <c r="Z52" s="26"/>
-      <c r="AA52" s="26"/>
-      <c r="AB52" s="26"/>
-      <c r="AC52" s="26"/>
+      <c r="B52" s="27"/>
+      <c r="C52" s="27"/>
+      <c r="D52" s="27"/>
+      <c r="E52" s="27"/>
+      <c r="F52" s="27"/>
+      <c r="G52" s="27"/>
+      <c r="H52" s="27"/>
+      <c r="I52" s="27"/>
+      <c r="J52" s="27"/>
+      <c r="K52" s="27"/>
+      <c r="L52" s="27"/>
+      <c r="M52" s="27"/>
+      <c r="N52" s="27"/>
+      <c r="O52" s="27"/>
+      <c r="P52" s="27"/>
+      <c r="Q52" s="27"/>
+      <c r="R52" s="27"/>
+      <c r="S52" s="27"/>
+      <c r="T52" s="27"/>
+      <c r="U52" s="27"/>
+      <c r="V52" s="27"/>
+      <c r="W52" s="27"/>
+      <c r="X52" s="27"/>
+      <c r="Y52" s="27"/>
+      <c r="Z52" s="27"/>
+      <c r="AA52" s="27"/>
+      <c r="AB52" s="27"/>
+      <c r="AC52" s="27"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="27" t="s">
+      <c r="A53" s="28" t="s">
         <v>311</v>
       </c>
-      <c r="B53" s="29">
+      <c r="B53" s="30">
         <v>15.79</v>
       </c>
-      <c r="C53" s="29">
+      <c r="C53" s="30">
         <v>19.12</v>
       </c>
-      <c r="D53" s="29">
+      <c r="D53" s="30">
         <v>12.6</v>
       </c>
-      <c r="E53" s="29">
+      <c r="E53" s="30">
         <v>12.05</v>
       </c>
-      <c r="F53" s="29">
+      <c r="F53" s="30">
         <v>10.97</v>
       </c>
-      <c r="G53" s="29">
+      <c r="G53" s="30">
         <v>25.39</v>
       </c>
-      <c r="H53" s="29">
+      <c r="H53" s="30">
         <v>10.92</v>
       </c>
-      <c r="I53" s="29">
+      <c r="I53" s="30">
         <v>10.0</v>
       </c>
-      <c r="J53" s="29">
+      <c r="J53" s="30">
         <v>11.72</v>
       </c>
-      <c r="K53" s="29">
+      <c r="K53" s="30">
         <v>11.75</v>
       </c>
-      <c r="L53" s="29">
+      <c r="L53" s="30">
         <v>19.37</v>
       </c>
-      <c r="M53" s="29">
+      <c r="M53" s="30">
         <v>12.37</v>
       </c>
-      <c r="N53" s="29">
+      <c r="N53" s="30">
         <v>15.3</v>
       </c>
-      <c r="O53" s="29">
+      <c r="O53" s="30">
         <v>7.82</v>
       </c>
-      <c r="P53" s="29">
+      <c r="P53" s="30">
         <v>10.51</v>
       </c>
-      <c r="Q53" s="29">
+      <c r="Q53" s="30">
         <v>5.94</v>
       </c>
-      <c r="R53" s="30"/>
-      <c r="S53" s="29">
+      <c r="R53" s="31"/>
+      <c r="S53" s="30">
         <v>9.21</v>
       </c>
-      <c r="T53" s="29">
+      <c r="T53" s="30">
         <v>10.98</v>
       </c>
-      <c r="U53" s="29">
+      <c r="U53" s="30">
         <v>12.67</v>
       </c>
-      <c r="V53" s="29">
+      <c r="V53" s="30">
         <v>12.1</v>
       </c>
-      <c r="W53" s="29">
+      <c r="W53" s="30">
         <v>8.05</v>
       </c>
-      <c r="X53" s="29">
+      <c r="X53" s="30">
         <v>8.57</v>
       </c>
-      <c r="Y53" s="29">
+      <c r="Y53" s="30">
         <v>4.06</v>
       </c>
-      <c r="Z53" s="29">
+      <c r="Z53" s="30">
         <v>4.85</v>
       </c>
-      <c r="AA53" s="29">
+      <c r="AA53" s="30">
         <v>6.47</v>
       </c>
-      <c r="AB53" s="29">
+      <c r="AB53" s="30">
         <v>6.13</v>
       </c>
-      <c r="AC53" s="29">
+      <c r="AC53" s="30">
         <v>6.38</v>
       </c>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="27" t="s">
+      <c r="A54" s="28" t="s">
         <v>312</v>
       </c>
-      <c r="B54" s="29">
+      <c r="B54" s="30">
         <v>13.7</v>
       </c>
-      <c r="C54" s="29">
+      <c r="C54" s="30">
         <v>14.18</v>
       </c>
-      <c r="D54" s="29">
+      <c r="D54" s="30">
         <v>12.73</v>
       </c>
-      <c r="E54" s="29">
+      <c r="E54" s="30">
         <v>12.12</v>
       </c>
-      <c r="F54" s="29">
+      <c r="F54" s="30">
         <v>12.07</v>
       </c>
-      <c r="G54" s="29">
+      <c r="G54" s="30">
         <v>12.31</v>
       </c>
-      <c r="H54" s="29">
+      <c r="H54" s="30">
         <v>12.08</v>
       </c>
-      <c r="I54" s="29">
+      <c r="I54" s="30">
         <v>12.38</v>
       </c>
-      <c r="J54" s="29">
+      <c r="J54" s="30">
         <v>13.56</v>
       </c>
-      <c r="K54" s="29">
+      <c r="K54" s="30">
         <v>12.6</v>
       </c>
-      <c r="L54" s="29">
+      <c r="L54" s="30">
         <v>12.42</v>
       </c>
-      <c r="M54" s="29">
+      <c r="M54" s="30">
         <v>10.07</v>
       </c>
-      <c r="N54" s="29">
+      <c r="N54" s="30">
         <v>11.52</v>
       </c>
-      <c r="O54" s="29">
+      <c r="O54" s="30">
         <v>10.26</v>
       </c>
-      <c r="P54" s="29">
+      <c r="P54" s="30">
         <v>11.26</v>
       </c>
-      <c r="Q54" s="29">
+      <c r="Q54" s="30">
         <v>11.8</v>
       </c>
-      <c r="R54" s="29">
+      <c r="R54" s="30">
         <v>13.18</v>
       </c>
-      <c r="S54" s="29">
+      <c r="S54" s="30">
         <v>10.76</v>
       </c>
-      <c r="T54" s="29">
+      <c r="T54" s="30">
         <v>10.97</v>
       </c>
-      <c r="U54" s="29">
+      <c r="U54" s="30">
         <v>9.3</v>
       </c>
-      <c r="V54" s="29">
+      <c r="V54" s="30">
         <v>7.14</v>
       </c>
-      <c r="W54" s="29">
+      <c r="W54" s="30">
         <v>5.91</v>
       </c>
-      <c r="X54" s="29">
+      <c r="X54" s="30">
         <v>5.64</v>
       </c>
-      <c r="Y54" s="29">
+      <c r="Y54" s="30">
         <v>5.45</v>
       </c>
-      <c r="Z54" s="30"/>
-      <c r="AA54" s="30"/>
-      <c r="AB54" s="30"/>
-      <c r="AC54" s="30"/>
+      <c r="Z54" s="31"/>
+      <c r="AA54" s="31"/>
+      <c r="AB54" s="31"/>
+      <c r="AC54" s="31"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="25" t="s">
+      <c r="A55" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="B55" s="26"/>
-      <c r="C55" s="26"/>
-      <c r="D55" s="26"/>
-      <c r="E55" s="26"/>
-      <c r="F55" s="26"/>
-      <c r="G55" s="26"/>
-      <c r="H55" s="26"/>
-      <c r="I55" s="26"/>
-      <c r="J55" s="26"/>
-      <c r="K55" s="26"/>
-      <c r="L55" s="26"/>
-      <c r="M55" s="26"/>
-      <c r="N55" s="26"/>
-      <c r="O55" s="26"/>
-      <c r="P55" s="26"/>
-      <c r="Q55" s="26"/>
-      <c r="R55" s="26"/>
-      <c r="S55" s="26"/>
-      <c r="T55" s="26"/>
-      <c r="U55" s="26"/>
-      <c r="V55" s="26"/>
-      <c r="W55" s="26"/>
-      <c r="X55" s="26"/>
-      <c r="Y55" s="26"/>
-      <c r="Z55" s="26"/>
-      <c r="AA55" s="26"/>
-      <c r="AB55" s="26"/>
-      <c r="AC55" s="26"/>
+      <c r="B55" s="27"/>
+      <c r="C55" s="27"/>
+      <c r="D55" s="27"/>
+      <c r="E55" s="27"/>
+      <c r="F55" s="27"/>
+      <c r="G55" s="27"/>
+      <c r="H55" s="27"/>
+      <c r="I55" s="27"/>
+      <c r="J55" s="27"/>
+      <c r="K55" s="27"/>
+      <c r="L55" s="27"/>
+      <c r="M55" s="27"/>
+      <c r="N55" s="27"/>
+      <c r="O55" s="27"/>
+      <c r="P55" s="27"/>
+      <c r="Q55" s="27"/>
+      <c r="R55" s="27"/>
+      <c r="S55" s="27"/>
+      <c r="T55" s="27"/>
+      <c r="U55" s="27"/>
+      <c r="V55" s="27"/>
+      <c r="W55" s="27"/>
+      <c r="X55" s="27"/>
+      <c r="Y55" s="27"/>
+      <c r="Z55" s="27"/>
+      <c r="AA55" s="27"/>
+      <c r="AB55" s="27"/>
+      <c r="AC55" s="27"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="27" t="s">
+      <c r="A56" s="28" t="s">
         <v>314</v>
       </c>
-      <c r="B56" s="29">
+      <c r="B56" s="30">
         <v>15.79</v>
       </c>
-      <c r="C56" s="29">
+      <c r="C56" s="30">
         <v>19.12</v>
       </c>
-      <c r="D56" s="29">
+      <c r="D56" s="30">
         <v>12.6</v>
       </c>
-      <c r="E56" s="29">
+      <c r="E56" s="30">
         <v>12.05</v>
       </c>
-      <c r="F56" s="29">
+      <c r="F56" s="30">
         <v>10.97</v>
       </c>
-      <c r="G56" s="29">
+      <c r="G56" s="30">
         <v>25.39</v>
       </c>
-      <c r="H56" s="29">
+      <c r="H56" s="30">
         <v>10.92</v>
       </c>
-      <c r="I56" s="29">
+      <c r="I56" s="30">
         <v>10.0</v>
       </c>
-      <c r="J56" s="29">
+      <c r="J56" s="30">
         <v>11.72</v>
       </c>
-      <c r="K56" s="29">
+      <c r="K56" s="30">
         <v>11.75</v>
       </c>
-      <c r="L56" s="29">
+      <c r="L56" s="30">
         <v>19.37</v>
       </c>
-      <c r="M56" s="29">
+      <c r="M56" s="30">
         <v>12.37</v>
       </c>
-      <c r="N56" s="29">
+      <c r="N56" s="30">
         <v>15.3</v>
       </c>
-      <c r="O56" s="29">
+      <c r="O56" s="30">
         <v>7.82</v>
       </c>
-      <c r="P56" s="29">
+      <c r="P56" s="30">
         <v>10.51</v>
       </c>
-      <c r="Q56" s="29">
+      <c r="Q56" s="30">
         <v>5.94</v>
       </c>
-      <c r="R56" s="30"/>
-      <c r="S56" s="29">
+      <c r="R56" s="31"/>
+      <c r="S56" s="30">
         <v>13.07</v>
       </c>
-      <c r="T56" s="29">
+      <c r="T56" s="30">
         <v>15.22</v>
       </c>
-      <c r="U56" s="29">
+      <c r="U56" s="30">
         <v>19.53</v>
       </c>
-      <c r="V56" s="29">
+      <c r="V56" s="30">
         <v>11.45</v>
       </c>
-      <c r="W56" s="29">
+      <c r="W56" s="30">
         <v>7.72</v>
       </c>
-      <c r="X56" s="29">
+      <c r="X56" s="30">
         <v>8.12</v>
       </c>
-      <c r="Y56" s="29">
+      <c r="Y56" s="30">
         <v>4.06</v>
       </c>
-      <c r="Z56" s="29">
+      <c r="Z56" s="30">
         <v>4.85</v>
       </c>
-      <c r="AA56" s="29">
+      <c r="AA56" s="30">
         <v>6.47</v>
       </c>
-      <c r="AB56" s="29">
+      <c r="AB56" s="30">
         <v>6.13</v>
       </c>
-      <c r="AC56" s="29">
+      <c r="AC56" s="30">
         <v>6.38</v>
       </c>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="27" t="s">
+      <c r="A57" s="28" t="s">
         <v>315</v>
       </c>
-      <c r="B57" s="29">
+      <c r="B57" s="30">
         <v>1.81</v>
       </c>
-      <c r="C57" s="29">
+      <c r="C57" s="30">
         <v>1.77</v>
       </c>
-      <c r="D57" s="29">
+      <c r="D57" s="30">
         <v>1.69</v>
       </c>
-      <c r="E57" s="29">
+      <c r="E57" s="30">
         <v>1.73</v>
       </c>
-      <c r="F57" s="29">
+      <c r="F57" s="30">
         <v>1.68</v>
       </c>
-      <c r="G57" s="29">
+      <c r="G57" s="30">
         <v>1.76</v>
       </c>
-      <c r="H57" s="29">
+      <c r="H57" s="30">
         <v>1.98</v>
       </c>
-      <c r="I57" s="29">
+      <c r="I57" s="30">
         <v>2.14</v>
       </c>
-      <c r="J57" s="29">
+      <c r="J57" s="30">
         <v>2.2</v>
       </c>
-      <c r="K57" s="29">
+      <c r="K57" s="30">
         <v>2.22</v>
       </c>
-      <c r="L57" s="29">
+      <c r="L57" s="30">
         <v>2.17</v>
       </c>
-      <c r="M57" s="29">
+      <c r="M57" s="30">
         <v>1.77</v>
       </c>
-      <c r="N57" s="29">
+      <c r="N57" s="30">
         <v>1.61</v>
       </c>
-      <c r="O57" s="29">
+      <c r="O57" s="30">
         <v>1.38</v>
       </c>
-      <c r="P57" s="29">
+      <c r="P57" s="30">
         <v>1.28</v>
       </c>
-      <c r="Q57" s="29">
+      <c r="Q57" s="30">
         <v>1.26</v>
       </c>
-      <c r="R57" s="29">
+      <c r="R57" s="30">
         <v>1.33</v>
       </c>
-      <c r="S57" s="29">
+      <c r="S57" s="30">
         <v>1.23</v>
       </c>
-      <c r="T57" s="29">
+      <c r="T57" s="30">
         <v>1.16</v>
       </c>
-      <c r="U57" s="29">
+      <c r="U57" s="30">
         <v>1.01</v>
       </c>
-      <c r="V57" s="29">
+      <c r="V57" s="30">
         <v>0.89</v>
       </c>
-      <c r="W57" s="29">
+      <c r="W57" s="30">
         <v>0.76</v>
       </c>
-      <c r="X57" s="29">
+      <c r="X57" s="30">
         <v>0.8</v>
       </c>
-      <c r="Y57" s="29">
+      <c r="Y57" s="30">
         <v>0.86</v>
       </c>
-      <c r="Z57" s="30"/>
-      <c r="AA57" s="30"/>
-      <c r="AB57" s="30"/>
-      <c r="AC57" s="30"/>
+      <c r="Z57" s="31"/>
+      <c r="AA57" s="31"/>
+      <c r="AB57" s="31"/>
+      <c r="AC57" s="31"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="25" t="s">
+      <c r="A58" s="26" t="s">
         <v>316</v>
       </c>
-      <c r="B58" s="26"/>
-      <c r="C58" s="26"/>
-      <c r="D58" s="26"/>
-      <c r="E58" s="26"/>
-      <c r="F58" s="26"/>
-      <c r="G58" s="26"/>
-      <c r="H58" s="26"/>
-      <c r="I58" s="26"/>
-      <c r="J58" s="26"/>
-      <c r="K58" s="26"/>
-      <c r="L58" s="26"/>
-      <c r="M58" s="26"/>
-      <c r="N58" s="26"/>
-      <c r="O58" s="26"/>
-      <c r="P58" s="26"/>
-      <c r="Q58" s="26"/>
-      <c r="R58" s="26"/>
-      <c r="S58" s="26"/>
-      <c r="T58" s="26"/>
-      <c r="U58" s="26"/>
-      <c r="V58" s="26"/>
-      <c r="W58" s="26"/>
-      <c r="X58" s="26"/>
-      <c r="Y58" s="26"/>
-      <c r="Z58" s="26"/>
-      <c r="AA58" s="26"/>
-      <c r="AB58" s="26"/>
-      <c r="AC58" s="26"/>
+      <c r="B58" s="27"/>
+      <c r="C58" s="27"/>
+      <c r="D58" s="27"/>
+      <c r="E58" s="27"/>
+      <c r="F58" s="27"/>
+      <c r="G58" s="27"/>
+      <c r="H58" s="27"/>
+      <c r="I58" s="27"/>
+      <c r="J58" s="27"/>
+      <c r="K58" s="27"/>
+      <c r="L58" s="27"/>
+      <c r="M58" s="27"/>
+      <c r="N58" s="27"/>
+      <c r="O58" s="27"/>
+      <c r="P58" s="27"/>
+      <c r="Q58" s="27"/>
+      <c r="R58" s="27"/>
+      <c r="S58" s="27"/>
+      <c r="T58" s="27"/>
+      <c r="U58" s="27"/>
+      <c r="V58" s="27"/>
+      <c r="W58" s="27"/>
+      <c r="X58" s="27"/>
+      <c r="Y58" s="27"/>
+      <c r="Z58" s="27"/>
+      <c r="AA58" s="27"/>
+      <c r="AB58" s="27"/>
+      <c r="AC58" s="27"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="27" t="s">
+      <c r="A59" s="28" t="s">
         <v>317</v>
       </c>
-      <c r="B59" s="29">
+      <c r="B59" s="30">
         <v>0.73</v>
       </c>
-      <c r="C59" s="33">
+      <c r="C59" s="34">
         <v>-0.76</v>
       </c>
-      <c r="D59" s="33">
+      <c r="D59" s="34">
         <v>-0.89</v>
       </c>
-      <c r="E59" s="29">
+      <c r="E59" s="30">
         <v>1.45</v>
       </c>
-      <c r="F59" s="29">
+      <c r="F59" s="30">
         <v>0.05</v>
       </c>
-      <c r="G59" s="33">
+      <c r="G59" s="34">
         <v>-0.43</v>
       </c>
-      <c r="H59" s="33">
+      <c r="H59" s="34">
         <v>-0.52</v>
       </c>
-      <c r="I59" s="29">
+      <c r="I59" s="30">
         <v>0.34</v>
       </c>
-      <c r="J59" s="33">
+      <c r="J59" s="34">
         <v>-3.45</v>
       </c>
-      <c r="K59" s="29">
+      <c r="K59" s="30">
         <v>0.18</v>
       </c>
-      <c r="L59" s="33">
+      <c r="L59" s="34">
         <v>-1.11</v>
       </c>
-      <c r="M59" s="29">
+      <c r="M59" s="30">
         <v>0.31</v>
       </c>
-      <c r="N59" s="33">
+      <c r="N59" s="34">
         <v>-0.34</v>
       </c>
-      <c r="O59" s="29">
+      <c r="O59" s="30">
         <v>0.22</v>
       </c>
-      <c r="P59" s="29">
+      <c r="P59" s="30">
         <v>1.01</v>
       </c>
-      <c r="Q59" s="30">
-        <v>0.0</v>
-      </c>
-      <c r="R59" s="30"/>
-      <c r="S59" s="29">
+      <c r="Q59" s="31">
+        <v>0.0</v>
+      </c>
+      <c r="R59" s="31"/>
+      <c r="S59" s="30">
         <v>1.68</v>
       </c>
-      <c r="T59" s="29">
+      <c r="T59" s="30">
         <v>1.9</v>
       </c>
-      <c r="U59" s="29">
+      <c r="U59" s="30">
         <v>0.48</v>
       </c>
-      <c r="V59" s="29">
+      <c r="V59" s="30">
         <v>0.27</v>
       </c>
-      <c r="W59" s="29">
+      <c r="W59" s="30">
         <v>0.29</v>
       </c>
-      <c r="X59" s="33">
+      <c r="X59" s="34">
         <v>-0.17</v>
       </c>
-      <c r="Y59" s="33">
+      <c r="Y59" s="34">
         <v>-0.26</v>
       </c>
-      <c r="Z59" s="29">
+      <c r="Z59" s="30">
         <v>0.1</v>
       </c>
-      <c r="AA59" s="33">
+      <c r="AA59" s="34">
         <v>-3.24</v>
       </c>
-      <c r="AB59" s="29">
+      <c r="AB59" s="30">
         <v>0.6</v>
       </c>
-      <c r="AC59" s="30"/>
+      <c r="AC59" s="31"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="27" t="s">
+      <c r="A60" s="28" t="s">
         <v>318</v>
       </c>
-      <c r="B60" s="29">
+      <c r="B60" s="30">
         <v>0.63</v>
       </c>
-      <c r="C60" s="33">
+      <c r="C60" s="34">
         <v>-8.19</v>
       </c>
-      <c r="D60" s="33">
+      <c r="D60" s="34">
         <v>-17.86</v>
       </c>
-      <c r="E60" s="29">
+      <c r="E60" s="30">
         <v>1.54</v>
       </c>
-      <c r="F60" s="29">
+      <c r="F60" s="30">
         <v>2.23</v>
       </c>
-      <c r="G60" s="33">
+      <c r="G60" s="34">
         <v>-1.62</v>
       </c>
-      <c r="H60" s="29">
+      <c r="H60" s="30">
         <v>2.01</v>
       </c>
-      <c r="I60" s="29">
+      <c r="I60" s="30">
         <v>0.65</v>
       </c>
-      <c r="J60" s="29">
+      <c r="J60" s="30">
         <v>54.79</v>
       </c>
-      <c r="K60" s="29">
+      <c r="K60" s="30">
         <v>1.73</v>
       </c>
-      <c r="L60" s="33">
+      <c r="L60" s="34">
         <v>-14.44</v>
       </c>
-      <c r="M60" s="30"/>
-      <c r="N60" s="33">
+      <c r="M60" s="31"/>
+      <c r="N60" s="34">
         <v>-1.41</v>
       </c>
-      <c r="O60" s="29">
+      <c r="O60" s="30">
         <v>2.25</v>
       </c>
-      <c r="P60" s="33">
+      <c r="P60" s="34">
         <v>-22.84</v>
       </c>
-      <c r="Q60" s="29">
+      <c r="Q60" s="30">
         <v>5.38</v>
       </c>
-      <c r="R60" s="30"/>
-      <c r="S60" s="29">
+      <c r="R60" s="31"/>
+      <c r="S60" s="30">
         <v>0.51</v>
       </c>
-      <c r="T60" s="29">
+      <c r="T60" s="30">
         <v>2.85</v>
       </c>
-      <c r="U60" s="33">
+      <c r="U60" s="34">
         <v>-13.46</v>
       </c>
-      <c r="V60" s="29">
+      <c r="V60" s="30">
         <v>2.99</v>
       </c>
-      <c r="W60" s="33">
+      <c r="W60" s="34">
         <v>-1.11</v>
       </c>
-      <c r="X60" s="33">
+      <c r="X60" s="34">
         <v>-0.7</v>
       </c>
-      <c r="Y60" s="30"/>
-      <c r="Z60" s="30"/>
-      <c r="AA60" s="30"/>
-      <c r="AB60" s="30"/>
-      <c r="AC60" s="30"/>
+      <c r="Y60" s="31"/>
+      <c r="Z60" s="31"/>
+      <c r="AA60" s="31"/>
+      <c r="AB60" s="31"/>
+      <c r="AC60" s="31"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="25" t="s">
+      <c r="A61" s="26" t="s">
         <v>319</v>
       </c>
-      <c r="B61" s="26"/>
-      <c r="C61" s="26"/>
-      <c r="D61" s="26"/>
-      <c r="E61" s="26"/>
-      <c r="F61" s="26"/>
-      <c r="G61" s="26"/>
-      <c r="H61" s="26"/>
-      <c r="I61" s="26"/>
-      <c r="J61" s="26"/>
-      <c r="K61" s="26"/>
-      <c r="L61" s="26"/>
-      <c r="M61" s="26"/>
-      <c r="N61" s="26"/>
-      <c r="O61" s="26"/>
-      <c r="P61" s="26"/>
-      <c r="Q61" s="26"/>
-      <c r="R61" s="26"/>
-      <c r="S61" s="26"/>
-      <c r="T61" s="26"/>
-      <c r="U61" s="26"/>
-      <c r="V61" s="26"/>
-      <c r="W61" s="26"/>
-      <c r="X61" s="26"/>
-      <c r="Y61" s="26"/>
-      <c r="Z61" s="26"/>
-      <c r="AA61" s="26"/>
-      <c r="AB61" s="26"/>
-      <c r="AC61" s="26"/>
+      <c r="B61" s="27"/>
+      <c r="C61" s="27"/>
+      <c r="D61" s="27"/>
+      <c r="E61" s="27"/>
+      <c r="F61" s="27"/>
+      <c r="G61" s="27"/>
+      <c r="H61" s="27"/>
+      <c r="I61" s="27"/>
+      <c r="J61" s="27"/>
+      <c r="K61" s="27"/>
+      <c r="L61" s="27"/>
+      <c r="M61" s="27"/>
+      <c r="N61" s="27"/>
+      <c r="O61" s="27"/>
+      <c r="P61" s="27"/>
+      <c r="Q61" s="27"/>
+      <c r="R61" s="27"/>
+      <c r="S61" s="27"/>
+      <c r="T61" s="27"/>
+      <c r="U61" s="27"/>
+      <c r="V61" s="27"/>
+      <c r="W61" s="27"/>
+      <c r="X61" s="27"/>
+      <c r="Y61" s="27"/>
+      <c r="Z61" s="27"/>
+      <c r="AA61" s="27"/>
+      <c r="AB61" s="27"/>
+      <c r="AC61" s="27"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="27" t="s">
+      <c r="A62" s="28" t="s">
         <v>320</v>
       </c>
-      <c r="B62" s="29">
+      <c r="B62" s="30">
         <v>0.52</v>
       </c>
-      <c r="C62" s="29">
+      <c r="C62" s="30">
         <v>0.61</v>
       </c>
-      <c r="D62" s="29">
+      <c r="D62" s="30">
         <v>0.52</v>
       </c>
-      <c r="E62" s="29">
+      <c r="E62" s="30">
         <v>0.61</v>
       </c>
-      <c r="F62" s="29">
+      <c r="F62" s="30">
         <v>0.46</v>
       </c>
-      <c r="G62" s="29">
+      <c r="G62" s="30">
         <v>0.43</v>
       </c>
-      <c r="H62" s="29">
+      <c r="H62" s="30">
         <v>0.44</v>
       </c>
-      <c r="I62" s="29">
+      <c r="I62" s="30">
         <v>0.45</v>
       </c>
-      <c r="J62" s="29">
+      <c r="J62" s="30">
         <v>0.45</v>
       </c>
-      <c r="K62" s="29">
+      <c r="K62" s="30">
         <v>0.54</v>
       </c>
-      <c r="L62" s="29">
+      <c r="L62" s="30">
         <v>0.6</v>
       </c>
-      <c r="M62" s="29">
+      <c r="M62" s="30">
         <v>0.4</v>
       </c>
-      <c r="N62" s="29">
+      <c r="N62" s="30">
         <v>0.39</v>
       </c>
-      <c r="O62" s="29">
+      <c r="O62" s="30">
         <v>0.41</v>
       </c>
-      <c r="P62" s="29">
+      <c r="P62" s="30">
         <v>0.43</v>
       </c>
-      <c r="Q62" s="29">
+      <c r="Q62" s="30">
         <v>0.1</v>
       </c>
-      <c r="R62" s="29">
+      <c r="R62" s="30">
         <v>0.28</v>
       </c>
-      <c r="S62" s="29">
+      <c r="S62" s="30">
         <v>0.36</v>
       </c>
-      <c r="T62" s="29">
+      <c r="T62" s="30">
         <v>0.45</v>
       </c>
-      <c r="U62" s="29">
+      <c r="U62" s="30">
         <v>0.52</v>
       </c>
-      <c r="V62" s="29">
+      <c r="V62" s="30">
         <v>0.43</v>
       </c>
-      <c r="W62" s="29">
+      <c r="W62" s="30">
         <v>0.13</v>
       </c>
-      <c r="X62" s="29">
+      <c r="X62" s="30">
         <v>0.16</v>
       </c>
-      <c r="Y62" s="29">
+      <c r="Y62" s="30">
         <v>0.16</v>
       </c>
-      <c r="Z62" s="29">
+      <c r="Z62" s="30">
         <v>0.12</v>
       </c>
-      <c r="AA62" s="29">
+      <c r="AA62" s="30">
         <v>0.11</v>
       </c>
-      <c r="AB62" s="29">
+      <c r="AB62" s="30">
         <v>0.33</v>
       </c>
-      <c r="AC62" s="29">
+      <c r="AC62" s="30">
         <v>0.42</v>
       </c>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="27" t="s">
+      <c r="A63" s="28" t="s">
         <v>321</v>
       </c>
-      <c r="B63" s="29">
+      <c r="B63" s="30">
         <v>0.55</v>
       </c>
-      <c r="C63" s="29">
+      <c r="C63" s="30">
         <v>0.54</v>
       </c>
-      <c r="D63" s="29">
+      <c r="D63" s="30">
         <v>0.5</v>
       </c>
-      <c r="E63" s="29">
+      <c r="E63" s="30">
         <v>0.48</v>
       </c>
-      <c r="F63" s="29">
+      <c r="F63" s="30">
         <v>0.45</v>
       </c>
-      <c r="G63" s="29">
+      <c r="G63" s="30">
         <v>0.46</v>
       </c>
-      <c r="H63" s="29">
+      <c r="H63" s="30">
         <v>0.49</v>
       </c>
-      <c r="I63" s="29">
+      <c r="I63" s="30">
         <v>0.48</v>
       </c>
-      <c r="J63" s="29">
+      <c r="J63" s="30">
         <v>0.48</v>
       </c>
-      <c r="K63" s="29">
+      <c r="K63" s="30">
         <v>0.47</v>
       </c>
-      <c r="L63" s="29">
+      <c r="L63" s="30">
         <v>0.45</v>
       </c>
-      <c r="M63" s="29">
+      <c r="M63" s="30">
         <v>0.35</v>
       </c>
-      <c r="N63" s="29">
+      <c r="N63" s="30">
         <v>0.33</v>
       </c>
-      <c r="O63" s="29">
+      <c r="O63" s="30">
         <v>0.32</v>
       </c>
-      <c r="P63" s="29">
+      <c r="P63" s="30">
         <v>0.33</v>
       </c>
-      <c r="Q63" s="29">
+      <c r="Q63" s="30">
         <v>0.35</v>
       </c>
-      <c r="R63" s="29">
+      <c r="R63" s="30">
         <v>0.41</v>
       </c>
-      <c r="S63" s="29">
+      <c r="S63" s="30">
         <v>0.39</v>
       </c>
-      <c r="T63" s="29">
+      <c r="T63" s="30">
         <v>0.36</v>
       </c>
-      <c r="U63" s="29">
+      <c r="U63" s="30">
         <v>0.3</v>
       </c>
-      <c r="V63" s="29">
+      <c r="V63" s="30">
         <v>0.2</v>
       </c>
-      <c r="W63" s="29">
+      <c r="W63" s="30">
         <v>0.13</v>
       </c>
-      <c r="X63" s="29">
+      <c r="X63" s="30">
         <v>0.18</v>
       </c>
-      <c r="Y63" s="29">
+      <c r="Y63" s="30">
         <v>0.23</v>
       </c>
-      <c r="Z63" s="30"/>
-      <c r="AA63" s="30"/>
-      <c r="AB63" s="30"/>
-      <c r="AC63" s="30"/>
+      <c r="Z63" s="31"/>
+      <c r="AA63" s="31"/>
+      <c r="AB63" s="31"/>
+      <c r="AC63" s="31"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="25" t="s">
+      <c r="A64" s="26" t="s">
         <v>322</v>
       </c>
-      <c r="B64" s="26"/>
-      <c r="C64" s="26"/>
-      <c r="D64" s="26"/>
-      <c r="E64" s="26"/>
-      <c r="F64" s="26"/>
-      <c r="G64" s="26"/>
-      <c r="H64" s="26"/>
-      <c r="I64" s="26"/>
-      <c r="J64" s="26"/>
-      <c r="K64" s="26"/>
-      <c r="L64" s="26"/>
-      <c r="M64" s="26"/>
-      <c r="N64" s="26"/>
-      <c r="O64" s="26"/>
-      <c r="P64" s="26"/>
-      <c r="Q64" s="26"/>
-      <c r="R64" s="26"/>
-      <c r="S64" s="26"/>
-      <c r="T64" s="26"/>
-      <c r="U64" s="26"/>
-      <c r="V64" s="26"/>
-      <c r="W64" s="26"/>
-      <c r="X64" s="26"/>
-      <c r="Y64" s="26"/>
-      <c r="Z64" s="26"/>
-      <c r="AA64" s="26"/>
-      <c r="AB64" s="26"/>
-      <c r="AC64" s="26"/>
+      <c r="B64" s="27"/>
+      <c r="C64" s="27"/>
+      <c r="D64" s="27"/>
+      <c r="E64" s="27"/>
+      <c r="F64" s="27"/>
+      <c r="G64" s="27"/>
+      <c r="H64" s="27"/>
+      <c r="I64" s="27"/>
+      <c r="J64" s="27"/>
+      <c r="K64" s="27"/>
+      <c r="L64" s="27"/>
+      <c r="M64" s="27"/>
+      <c r="N64" s="27"/>
+      <c r="O64" s="27"/>
+      <c r="P64" s="27"/>
+      <c r="Q64" s="27"/>
+      <c r="R64" s="27"/>
+      <c r="S64" s="27"/>
+      <c r="T64" s="27"/>
+      <c r="U64" s="27"/>
+      <c r="V64" s="27"/>
+      <c r="W64" s="27"/>
+      <c r="X64" s="27"/>
+      <c r="Y64" s="27"/>
+      <c r="Z64" s="27"/>
+      <c r="AA64" s="27"/>
+      <c r="AB64" s="27"/>
+      <c r="AC64" s="27"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="27" t="s">
+      <c r="A65" s="28" t="s">
         <v>323</v>
       </c>
-      <c r="B65" s="29">
+      <c r="B65" s="30">
         <v>5.29</v>
       </c>
-      <c r="C65" s="29">
+      <c r="C65" s="30">
         <v>6.16</v>
       </c>
-      <c r="D65" s="29">
+      <c r="D65" s="30">
         <v>4.43</v>
       </c>
-      <c r="E65" s="29">
+      <c r="E65" s="30">
         <v>5.21</v>
       </c>
-      <c r="F65" s="29">
+      <c r="F65" s="30">
         <v>3.41</v>
       </c>
-      <c r="G65" s="29">
+      <c r="G65" s="30">
         <v>5.97</v>
       </c>
-      <c r="H65" s="29">
+      <c r="H65" s="30">
         <v>4.75</v>
       </c>
-      <c r="I65" s="29">
+      <c r="I65" s="30">
         <v>4.17</v>
       </c>
-      <c r="J65" s="29">
+      <c r="J65" s="30">
         <v>4.81</v>
       </c>
-      <c r="K65" s="29">
+      <c r="K65" s="30">
         <v>5.23</v>
       </c>
-      <c r="L65" s="29">
+      <c r="L65" s="30">
         <v>7.75</v>
       </c>
-      <c r="M65" s="29">
+      <c r="M65" s="30">
         <v>4.51</v>
       </c>
-      <c r="N65" s="29">
+      <c r="N65" s="30">
         <v>5.12</v>
       </c>
-      <c r="O65" s="29">
+      <c r="O65" s="30">
         <v>4.53</v>
       </c>
-      <c r="P65" s="29">
+      <c r="P65" s="30">
         <v>4.08</v>
       </c>
-      <c r="Q65" s="29">
+      <c r="Q65" s="30">
         <v>0.01</v>
       </c>
-      <c r="R65" s="29">
+      <c r="R65" s="30">
         <v>0.01</v>
       </c>
-      <c r="S65" s="29">
+      <c r="S65" s="30">
         <v>3.35</v>
       </c>
-      <c r="T65" s="29">
+      <c r="T65" s="30">
         <v>4.28</v>
       </c>
-      <c r="U65" s="29">
+      <c r="U65" s="30">
         <v>4.76</v>
       </c>
-      <c r="V65" s="29">
+      <c r="V65" s="30">
         <v>4.14</v>
       </c>
-      <c r="W65" s="29">
+      <c r="W65" s="30">
         <v>1.46</v>
       </c>
-      <c r="X65" s="29">
+      <c r="X65" s="30">
         <v>1.91</v>
       </c>
-      <c r="Y65" s="29">
+      <c r="Y65" s="30">
         <v>1.96</v>
       </c>
-      <c r="Z65" s="29">
+      <c r="Z65" s="30">
         <v>1.69</v>
       </c>
-      <c r="AA65" s="29">
+      <c r="AA65" s="30">
         <v>1.67</v>
       </c>
-      <c r="AB65" s="29">
+      <c r="AB65" s="30">
         <v>4.82</v>
       </c>
-      <c r="AC65" s="29">
+      <c r="AC65" s="30">
         <v>3.98</v>
       </c>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="27" t="s">
+      <c r="A66" s="28" t="s">
         <v>324</v>
       </c>
-      <c r="B66" s="29">
+      <c r="B66" s="30">
         <v>4.97</v>
       </c>
-      <c r="C66" s="29">
+      <c r="C66" s="30">
         <v>4.98</v>
       </c>
-      <c r="D66" s="29">
+      <c r="D66" s="30">
         <v>4.61</v>
       </c>
-      <c r="E66" s="29">
+      <c r="E66" s="30">
         <v>4.57</v>
       </c>
-      <c r="F66" s="29">
+      <c r="F66" s="30">
         <v>4.43</v>
       </c>
-      <c r="G66" s="29">
+      <c r="G66" s="30">
         <v>4.9</v>
       </c>
-      <c r="H66" s="29">
+      <c r="H66" s="30">
         <v>5.14</v>
       </c>
-      <c r="I66" s="29">
+      <c r="I66" s="30">
         <v>5.12</v>
       </c>
-      <c r="J66" s="29">
+      <c r="J66" s="30">
         <v>5.4</v>
       </c>
-      <c r="K66" s="29">
+      <c r="K66" s="30">
         <v>5.38</v>
       </c>
-      <c r="L66" s="29">
+      <c r="L66" s="30">
         <v>5.14</v>
       </c>
-      <c r="M66" s="29">
+      <c r="M66" s="30">
         <v>0.15</v>
       </c>
-      <c r="N66" s="29">
+      <c r="N66" s="30">
         <v>0.05</v>
       </c>
-      <c r="O66" s="29">
+      <c r="O66" s="30">
         <v>0.05</v>
       </c>
-      <c r="P66" s="29">
+      <c r="P66" s="30">
         <v>0.05</v>
       </c>
-      <c r="Q66" s="29">
+      <c r="Q66" s="30">
         <v>0.06</v>
       </c>
-      <c r="R66" s="29">
+      <c r="R66" s="30">
         <v>0.1</v>
       </c>
-      <c r="S66" s="29">
+      <c r="S66" s="30">
         <v>3.76</v>
       </c>
-      <c r="T66" s="29">
+      <c r="T66" s="30">
         <v>3.62</v>
       </c>
-      <c r="U66" s="29">
+      <c r="U66" s="30">
         <v>3.13</v>
       </c>
-      <c r="V66" s="29">
+      <c r="V66" s="30">
         <v>2.33</v>
       </c>
-      <c r="W66" s="29">
+      <c r="W66" s="30">
         <v>1.74</v>
       </c>
-      <c r="X66" s="29">
+      <c r="X66" s="30">
         <v>2.44</v>
       </c>
-      <c r="Y66" s="29">
+      <c r="Y66" s="30">
         <v>2.92</v>
       </c>
-      <c r="Z66" s="30"/>
-      <c r="AA66" s="30"/>
-      <c r="AB66" s="30"/>
-      <c r="AC66" s="30"/>
+      <c r="Z66" s="31"/>
+      <c r="AA66" s="31"/>
+      <c r="AB66" s="31"/>
+      <c r="AC66" s="31"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="25" t="s">
+      <c r="A67" s="26" t="s">
         <v>325</v>
       </c>
-      <c r="B67" s="26"/>
-      <c r="C67" s="26"/>
-      <c r="D67" s="26"/>
-      <c r="E67" s="26"/>
-      <c r="F67" s="26"/>
-      <c r="G67" s="26"/>
-      <c r="H67" s="26"/>
-      <c r="I67" s="26"/>
-      <c r="J67" s="26"/>
-      <c r="K67" s="26"/>
-      <c r="L67" s="26"/>
-      <c r="M67" s="26"/>
-      <c r="N67" s="26"/>
-      <c r="O67" s="26"/>
-      <c r="P67" s="26"/>
-      <c r="Q67" s="26"/>
-      <c r="R67" s="26"/>
-      <c r="S67" s="26"/>
-      <c r="T67" s="26"/>
-      <c r="U67" s="26"/>
-      <c r="V67" s="26"/>
-      <c r="W67" s="26"/>
-      <c r="X67" s="26"/>
-      <c r="Y67" s="26"/>
-      <c r="Z67" s="26"/>
-      <c r="AA67" s="26"/>
-      <c r="AB67" s="26"/>
-      <c r="AC67" s="26"/>
+      <c r="B67" s="27"/>
+      <c r="C67" s="27"/>
+      <c r="D67" s="27"/>
+      <c r="E67" s="27"/>
+      <c r="F67" s="27"/>
+      <c r="G67" s="27"/>
+      <c r="H67" s="27"/>
+      <c r="I67" s="27"/>
+      <c r="J67" s="27"/>
+      <c r="K67" s="27"/>
+      <c r="L67" s="27"/>
+      <c r="M67" s="27"/>
+      <c r="N67" s="27"/>
+      <c r="O67" s="27"/>
+      <c r="P67" s="27"/>
+      <c r="Q67" s="27"/>
+      <c r="R67" s="27"/>
+      <c r="S67" s="27"/>
+      <c r="T67" s="27"/>
+      <c r="U67" s="27"/>
+      <c r="V67" s="27"/>
+      <c r="W67" s="27"/>
+      <c r="X67" s="27"/>
+      <c r="Y67" s="27"/>
+      <c r="Z67" s="27"/>
+      <c r="AA67" s="27"/>
+      <c r="AB67" s="27"/>
+      <c r="AC67" s="27"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="27" t="s">
+      <c r="A68" s="28" t="s">
         <v>326</v>
       </c>
-      <c r="B68" s="29">
+      <c r="B68" s="30">
         <v>6.85</v>
       </c>
-      <c r="C68" s="29">
+      <c r="C68" s="30">
         <v>7.58</v>
       </c>
-      <c r="D68" s="29">
+      <c r="D68" s="30">
         <v>8.54</v>
       </c>
-      <c r="E68" s="28">
+      <c r="E68" s="29">
         <v>109.08</v>
       </c>
-      <c r="F68" s="29">
+      <c r="F68" s="30">
         <v>3.76</v>
       </c>
-      <c r="G68" s="29">
+      <c r="G68" s="30">
         <v>3.42</v>
       </c>
-      <c r="H68" s="29">
+      <c r="H68" s="30">
         <v>70.54</v>
       </c>
-      <c r="I68" s="29">
+      <c r="I68" s="30">
         <v>5.83</v>
       </c>
-      <c r="J68" s="29">
+      <c r="J68" s="30">
         <v>5.8</v>
       </c>
-      <c r="K68" s="29">
+      <c r="K68" s="30">
         <v>13.85</v>
       </c>
-      <c r="L68" s="29">
+      <c r="L68" s="30">
         <v>42.55</v>
       </c>
-      <c r="M68" s="29">
+      <c r="M68" s="30">
         <v>5.63</v>
       </c>
-      <c r="N68" s="29">
+      <c r="N68" s="30">
         <v>4.5</v>
       </c>
-      <c r="O68" s="29">
+      <c r="O68" s="30">
         <v>10.72</v>
       </c>
-      <c r="P68" s="28">
+      <c r="P68" s="29">
         <v>109.58</v>
       </c>
-      <c r="Q68" s="29">
+      <c r="Q68" s="30">
         <v>0.85</v>
       </c>
-      <c r="R68" s="29">
+      <c r="R68" s="30">
         <v>2.16</v>
       </c>
-      <c r="S68" s="29">
+      <c r="S68" s="30">
         <v>4.66</v>
       </c>
-      <c r="T68" s="29">
+      <c r="T68" s="30">
         <v>11.03</v>
       </c>
-      <c r="U68" s="29">
+      <c r="U68" s="30">
         <v>13.02</v>
       </c>
-      <c r="V68" s="29">
+      <c r="V68" s="30">
         <v>17.58</v>
       </c>
-      <c r="W68" s="29">
+      <c r="W68" s="30">
         <v>1.44</v>
       </c>
-      <c r="X68" s="29">
+      <c r="X68" s="30">
         <v>2.0</v>
       </c>
-      <c r="Y68" s="29">
+      <c r="Y68" s="30">
         <v>2.9</v>
       </c>
-      <c r="Z68" s="29">
+      <c r="Z68" s="30">
         <v>3.29</v>
       </c>
-      <c r="AA68" s="29">
+      <c r="AA68" s="30">
         <v>0.97</v>
       </c>
-      <c r="AB68" s="30"/>
-      <c r="AC68" s="29">
+      <c r="AB68" s="31"/>
+      <c r="AC68" s="30">
         <v>3.7</v>
       </c>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="27" t="s">
+      <c r="A69" s="28" t="s">
         <v>327</v>
       </c>
-      <c r="B69" s="29">
+      <c r="B69" s="30">
         <v>7.97</v>
       </c>
-      <c r="C69" s="29">
+      <c r="C69" s="30">
         <v>7.16</v>
       </c>
-      <c r="D69" s="29">
+      <c r="D69" s="30">
         <v>8.25</v>
       </c>
-      <c r="E69" s="29">
+      <c r="E69" s="30">
         <v>7.6</v>
       </c>
-      <c r="F69" s="29">
+      <c r="F69" s="30">
         <v>5.55</v>
       </c>
-      <c r="G69" s="29">
+      <c r="G69" s="30">
         <v>7.2</v>
       </c>
-      <c r="H69" s="29">
+      <c r="H69" s="30">
         <v>11.28</v>
       </c>
-      <c r="I69" s="29">
+      <c r="I69" s="30">
         <v>8.53</v>
       </c>
-      <c r="J69" s="29">
+      <c r="J69" s="30">
         <v>8.3</v>
       </c>
-      <c r="K69" s="29">
+      <c r="K69" s="30">
         <v>9.59</v>
       </c>
-      <c r="L69" s="29">
+      <c r="L69" s="30">
         <v>10.35</v>
       </c>
-      <c r="M69" s="29">
+      <c r="M69" s="30">
         <v>5.71</v>
       </c>
-      <c r="N69" s="29">
+      <c r="N69" s="30">
         <v>4.54</v>
       </c>
-      <c r="O69" s="29">
+      <c r="O69" s="30">
         <v>4.59</v>
       </c>
-      <c r="P69" s="29">
+      <c r="P69" s="30">
         <v>4.69</v>
       </c>
-      <c r="Q69" s="29">
+      <c r="Q69" s="30">
         <v>4.51</v>
       </c>
-      <c r="R69" s="29">
+      <c r="R69" s="30">
         <v>6.53</v>
       </c>
-      <c r="S69" s="29">
+      <c r="S69" s="30">
         <v>7.19</v>
       </c>
-      <c r="T69" s="29">
+      <c r="T69" s="30">
         <v>6.87</v>
       </c>
-      <c r="U69" s="29">
+      <c r="U69" s="30">
         <v>5.27</v>
       </c>
-      <c r="V69" s="29">
+      <c r="V69" s="30">
         <v>3.59</v>
       </c>
-      <c r="W69" s="29">
+      <c r="W69" s="30">
         <v>1.81</v>
       </c>
-      <c r="X69" s="29">
+      <c r="X69" s="30">
         <v>5.33</v>
       </c>
-      <c r="Y69" s="29">
+      <c r="Y69" s="30">
         <v>5.46</v>
       </c>
-      <c r="Z69" s="30"/>
-      <c r="AA69" s="30"/>
-      <c r="AB69" s="30"/>
-      <c r="AC69" s="30"/>
+      <c r="Z69" s="31"/>
+      <c r="AA69" s="31"/>
+      <c r="AB69" s="31"/>
+      <c r="AC69" s="31"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="25" t="s">
+      <c r="A70" s="26" t="s">
         <v>328</v>
       </c>
-      <c r="B70" s="26"/>
-      <c r="C70" s="26"/>
-      <c r="D70" s="26"/>
-      <c r="E70" s="26"/>
-      <c r="F70" s="26"/>
-      <c r="G70" s="26"/>
-      <c r="H70" s="26"/>
-      <c r="I70" s="26"/>
-      <c r="J70" s="26"/>
-      <c r="K70" s="26"/>
-      <c r="L70" s="26"/>
-      <c r="M70" s="26"/>
-      <c r="N70" s="26"/>
-      <c r="O70" s="26"/>
-      <c r="P70" s="26"/>
-      <c r="Q70" s="26"/>
-      <c r="R70" s="26"/>
-      <c r="S70" s="26"/>
-      <c r="T70" s="26"/>
-      <c r="U70" s="26"/>
-      <c r="V70" s="26"/>
-      <c r="W70" s="26"/>
-      <c r="X70" s="26"/>
-      <c r="Y70" s="26"/>
-      <c r="Z70" s="26"/>
-      <c r="AA70" s="26"/>
-      <c r="AB70" s="26"/>
-      <c r="AC70" s="26"/>
+      <c r="B70" s="27"/>
+      <c r="C70" s="27"/>
+      <c r="D70" s="27"/>
+      <c r="E70" s="27"/>
+      <c r="F70" s="27"/>
+      <c r="G70" s="27"/>
+      <c r="H70" s="27"/>
+      <c r="I70" s="27"/>
+      <c r="J70" s="27"/>
+      <c r="K70" s="27"/>
+      <c r="L70" s="27"/>
+      <c r="M70" s="27"/>
+      <c r="N70" s="27"/>
+      <c r="O70" s="27"/>
+      <c r="P70" s="27"/>
+      <c r="Q70" s="27"/>
+      <c r="R70" s="27"/>
+      <c r="S70" s="27"/>
+      <c r="T70" s="27"/>
+      <c r="U70" s="27"/>
+      <c r="V70" s="27"/>
+      <c r="W70" s="27"/>
+      <c r="X70" s="27"/>
+      <c r="Y70" s="27"/>
+      <c r="Z70" s="27"/>
+      <c r="AA70" s="27"/>
+      <c r="AB70" s="27"/>
+      <c r="AC70" s="27"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="27" t="s">
+      <c r="A71" s="28" t="s">
         <v>329</v>
       </c>
-      <c r="B71" s="29">
+      <c r="B71" s="30">
         <v>8.13</v>
       </c>
-      <c r="C71" s="29">
+      <c r="C71" s="30">
         <v>8.46</v>
       </c>
-      <c r="D71" s="29">
+      <c r="D71" s="30">
         <v>10.84</v>
       </c>
-      <c r="E71" s="30"/>
-      <c r="F71" s="29">
+      <c r="E71" s="31"/>
+      <c r="F71" s="30">
         <v>3.91</v>
       </c>
-      <c r="G71" s="29">
+      <c r="G71" s="30">
         <v>3.96</v>
       </c>
-      <c r="H71" s="30"/>
-      <c r="I71" s="29">
+      <c r="H71" s="31"/>
+      <c r="I71" s="30">
         <v>10.43</v>
       </c>
-      <c r="J71" s="29">
+      <c r="J71" s="30">
         <v>6.97</v>
       </c>
-      <c r="K71" s="29">
+      <c r="K71" s="30">
         <v>22.93</v>
       </c>
-      <c r="L71" s="30"/>
-      <c r="M71" s="29">
+      <c r="L71" s="31"/>
+      <c r="M71" s="30">
         <v>6.68</v>
       </c>
-      <c r="N71" s="29">
+      <c r="N71" s="30">
         <v>4.92</v>
       </c>
-      <c r="O71" s="29">
+      <c r="O71" s="30">
         <v>15.07</v>
       </c>
-      <c r="P71" s="30"/>
-      <c r="Q71" s="29">
+      <c r="P71" s="31"/>
+      <c r="Q71" s="30">
         <v>1.04</v>
       </c>
-      <c r="R71" s="29">
+      <c r="R71" s="30">
         <v>3.31</v>
       </c>
-      <c r="S71" s="29">
+      <c r="S71" s="30">
         <v>6.37</v>
       </c>
-      <c r="T71" s="29">
+      <c r="T71" s="30">
         <v>40.79</v>
       </c>
-      <c r="U71" s="30"/>
-      <c r="V71" s="30"/>
-      <c r="W71" s="29">
+      <c r="U71" s="31"/>
+      <c r="V71" s="31"/>
+      <c r="W71" s="30">
         <v>1.59</v>
       </c>
-      <c r="X71" s="29">
+      <c r="X71" s="30">
         <v>5.06</v>
       </c>
-      <c r="Y71" s="29">
+      <c r="Y71" s="30">
         <v>3.65</v>
       </c>
-      <c r="Z71" s="29">
+      <c r="Z71" s="30">
         <v>76.15</v>
       </c>
-      <c r="AA71" s="29">
+      <c r="AA71" s="30">
         <v>1.13</v>
       </c>
-      <c r="AB71" s="30"/>
-      <c r="AC71" s="29">
+      <c r="AB71" s="31"/>
+      <c r="AC71" s="30">
         <v>3.99</v>
       </c>
     </row>
     <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="27" t="s">
+      <c r="A72" s="28" t="s">
         <v>330</v>
       </c>
-      <c r="B72" s="29">
+      <c r="B72" s="30">
         <v>9.39</v>
       </c>
-      <c r="C72" s="29">
+      <c r="C72" s="30">
         <v>8.38</v>
       </c>
-      <c r="D72" s="29">
+      <c r="D72" s="30">
         <v>11.13</v>
       </c>
-      <c r="E72" s="29">
+      <c r="E72" s="30">
         <v>11.07</v>
       </c>
-      <c r="F72" s="29">
+      <c r="F72" s="30">
         <v>7.42</v>
       </c>
-      <c r="G72" s="29">
+      <c r="G72" s="30">
         <v>11.11</v>
       </c>
-      <c r="H72" s="29">
+      <c r="H72" s="30">
         <v>43.5</v>
       </c>
-      <c r="I72" s="29">
+      <c r="I72" s="30">
         <v>17.26</v>
       </c>
-      <c r="J72" s="29">
+      <c r="J72" s="30">
         <v>14.11</v>
       </c>
-      <c r="K72" s="29">
+      <c r="K72" s="30">
         <v>18.62</v>
       </c>
-      <c r="L72" s="29">
+      <c r="L72" s="30">
         <v>23.37</v>
       </c>
-      <c r="M72" s="29">
+      <c r="M72" s="30">
         <v>7.17</v>
       </c>
-      <c r="N72" s="29">
+      <c r="N72" s="30">
         <v>6.17</v>
       </c>
-      <c r="O72" s="29">
+      <c r="O72" s="30">
         <v>6.66</v>
       </c>
-      <c r="P72" s="29">
+      <c r="P72" s="30">
         <v>7.41</v>
       </c>
-      <c r="Q72" s="29">
+      <c r="Q72" s="30">
         <v>7.71</v>
       </c>
-      <c r="R72" s="29">
+      <c r="R72" s="30">
         <v>15.46</v>
       </c>
-      <c r="S72" s="29">
+      <c r="S72" s="30">
         <v>16.16</v>
       </c>
-      <c r="T72" s="29">
+      <c r="T72" s="30">
         <v>21.27</v>
       </c>
-      <c r="U72" s="29">
+      <c r="U72" s="30">
         <v>12.34</v>
       </c>
-      <c r="V72" s="29">
+      <c r="V72" s="30">
         <v>7.67</v>
       </c>
-      <c r="W72" s="29">
+      <c r="W72" s="30">
         <v>2.68</v>
       </c>
-      <c r="X72" s="29">
+      <c r="X72" s="30">
         <v>23.87</v>
       </c>
-      <c r="Y72" s="29">
+      <c r="Y72" s="30">
         <v>10.18</v>
       </c>
-      <c r="Z72" s="30"/>
-      <c r="AA72" s="30"/>
-      <c r="AB72" s="30"/>
-      <c r="AC72" s="30"/>
+      <c r="Z72" s="31"/>
+      <c r="AA72" s="31"/>
+      <c r="AB72" s="31"/>
+      <c r="AC72" s="31"/>
     </row>
     <row r="73" ht="15.75" customHeight="1"/>
     <row r="74" ht="15.75" customHeight="1"/>
